--- a/real_data/crm_template.xlsx
+++ b/real_data/crm_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralgi\dev\personal_crm\real_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B4171C-867A-476A-94B0-E5C855AA7511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC32E471-62AC-4278-9F50-64CA89D9EB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="61">
   <si>
     <t>Personal CRM — Data Entry Template</t>
   </si>
@@ -35,7 +35,13 @@
     <t>id column</t>
   </si>
   <si>
+    <t>Assign your own temporary integer IDs (1, 2, 3...). Used only to link records within Excel. Replaced by MySQL's real auto-incremented IDs on import.</t>
+  </si>
+  <si>
     <t>created_at column</t>
+  </si>
+  <si>
+    <t>Leave blank (assigned automatically by MySQL)</t>
   </si>
   <si>
     <t>Dates</t>
@@ -45,6 +51,21 @@
   </si>
   <si>
     <t>Dropdowns</t>
+  </si>
+  <si>
+    <t>Use the dropdown where provided</t>
+  </si>
+  <si>
+    <t>Import order</t>
+  </si>
+  <si>
+    <t>Python imports in this order: Companies → Contacts → Interactions → Referrals. Temp IDs are mapped to real MySQL IDs automatically.</t>
+  </si>
+  <si>
+    <t>import_to_mysql.py</t>
+  </si>
+  <si>
+    <t>Run this script to import Excel data into MySQL. It handles ID mapping so you never need to worry about real vs. temp IDs.</t>
   </si>
   <si>
     <t>COMPANIES</t>
@@ -187,21 +208,15 @@
   <si>
     <t>outcome</t>
   </si>
-  <si>
-    <t>Leave blank when entering new rows (assigned by MySQL on import)</t>
-  </si>
-  <si>
-    <t>Leave blank (assigned automatically by MySQL)</t>
-  </si>
-  <si>
-    <t>Use the dropdown where provided</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[&lt;=9999999]###\-####;\(###\)\ ###\-####"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,8 +245,21 @@
       <color rgb="FF2D4A6E"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,6 +279,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -278,10 +312,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -301,8 +336,57 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -606,205 +690,221 @@
   <sheetPr>
     <tabColor rgb="FF888888"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="83.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B7" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5"/>
-    </row>
-    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B9" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B10" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5"/>
-    </row>
-    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B13" s="5"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B18" s="5"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5"/>
     </row>
-    <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5"/>
     </row>
-    <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -820,10 +920,10 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12" style="22" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
@@ -832,35 +932,35 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>10</v>
+      <c r="D1" s="20" t="s">
+        <v>17</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -870,7 +970,7 @@
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
@@ -880,7 +980,7 @@
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -890,7 +990,7 @@
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -898,9 +998,9 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -908,9 +1008,9 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -918,19 +1018,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="26"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="G8" s="17"/>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -938,9 +1038,9 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -950,7 +1050,7 @@
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -960,7 +1060,7 @@
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -970,7 +1070,7 @@
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
@@ -980,7 +1080,7 @@
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -990,7 +1090,7 @@
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
@@ -1000,7 +1100,7 @@
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1010,7 +1110,7 @@
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
@@ -1020,7 +1120,7 @@
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -1030,7 +1130,7 @@
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
@@ -1040,7 +1140,7 @@
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -1050,7 +1150,7 @@
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
@@ -1060,7 +1160,7 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -1070,7 +1170,7 @@
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
@@ -1080,7 +1180,7 @@
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -1090,7 +1190,7 @@
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
@@ -1100,7 +1200,7 @@
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -1110,7 +1210,7 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -1120,7 +1220,7 @@
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -1130,7 +1230,7 @@
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
@@ -1140,7 +1240,7 @@
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
@@ -1150,7 +1250,7 @@
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
@@ -1160,7 +1260,7 @@
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
@@ -1170,7 +1270,7 @@
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
@@ -1180,7 +1280,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
@@ -1190,7 +1290,7 @@
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
@@ -1200,7 +1300,7 @@
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -1210,7 +1310,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
@@ -1220,7 +1320,7 @@
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -1230,7 +1330,7 @@
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
@@ -1240,7 +1340,7 @@
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
@@ -1250,7 +1350,7 @@
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
@@ -1260,7 +1360,7 @@
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -1270,7 +1370,7 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
@@ -1280,7 +1380,7 @@
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -1290,7 +1390,7 @@
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
@@ -1300,7 +1400,7 @@
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -1310,7 +1410,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
@@ -1320,7 +1420,7 @@
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -1330,7 +1430,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
@@ -1340,7 +1440,7 @@
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
@@ -1350,7 +1450,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
@@ -1360,7 +1460,7 @@
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -1370,7 +1470,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
@@ -1380,7 +1480,7 @@
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
@@ -1390,7 +1490,7 @@
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
@@ -1400,7 +1500,7 @@
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
@@ -1410,7 +1510,7 @@
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
@@ -1420,7 +1520,7 @@
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
+      <c r="D58" s="21"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
@@ -1430,7 +1530,7 @@
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
+      <c r="D59" s="21"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
@@ -1440,7 +1540,7 @@
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
+      <c r="D60" s="21"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
@@ -1450,7 +1550,7 @@
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
+      <c r="D61" s="21"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
@@ -1460,7 +1560,7 @@
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
+      <c r="D62" s="21"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -1470,7 +1570,7 @@
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
+      <c r="D63" s="21"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
@@ -1480,7 +1580,7 @@
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
+      <c r="D64" s="21"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
@@ -1490,7 +1590,7 @@
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
+      <c r="D65" s="21"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
@@ -1500,7 +1600,7 @@
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
+      <c r="D66" s="21"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
@@ -1510,7 +1610,7 @@
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
+      <c r="D67" s="21"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
@@ -1520,7 +1620,7 @@
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
+      <c r="D68" s="21"/>
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
@@ -1530,7 +1630,7 @@
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
+      <c r="D69" s="21"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
@@ -1540,7 +1640,7 @@
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
+      <c r="D70" s="21"/>
       <c r="E70" s="7"/>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
@@ -1550,7 +1650,7 @@
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
+      <c r="D71" s="21"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
@@ -1560,7 +1660,7 @@
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
+      <c r="D72" s="21"/>
       <c r="E72" s="7"/>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
@@ -1570,7 +1670,7 @@
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
+      <c r="D73" s="21"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
@@ -1580,7 +1680,7 @@
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
+      <c r="D74" s="21"/>
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
@@ -1590,7 +1690,7 @@
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
+      <c r="D75" s="21"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
@@ -1600,7 +1700,7 @@
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
+      <c r="D76" s="21"/>
       <c r="E76" s="7"/>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
@@ -1610,7 +1710,7 @@
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
+      <c r="D77" s="21"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
@@ -1620,7 +1720,7 @@
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
+      <c r="D78" s="21"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
@@ -1630,7 +1730,7 @@
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
+      <c r="D79" s="21"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
@@ -1640,7 +1740,7 @@
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
+      <c r="D80" s="21"/>
       <c r="E80" s="7"/>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
@@ -1650,7 +1750,7 @@
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
+      <c r="D81" s="21"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
@@ -1660,7 +1760,7 @@
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
+      <c r="D82" s="21"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
@@ -1670,7 +1770,7 @@
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
+      <c r="D83" s="21"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
@@ -1680,7 +1780,7 @@
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
+      <c r="D84" s="21"/>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
@@ -1690,7 +1790,7 @@
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
+      <c r="D85" s="21"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
@@ -1700,7 +1800,7 @@
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
+      <c r="D86" s="21"/>
       <c r="E86" s="7"/>
       <c r="F86" s="7"/>
       <c r="G86" s="7"/>
@@ -1710,7 +1810,7 @@
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
+      <c r="D87" s="21"/>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
@@ -1720,7 +1820,7 @@
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
+      <c r="D88" s="21"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -1730,7 +1830,7 @@
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
+      <c r="D89" s="21"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
@@ -1740,7 +1840,7 @@
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
+      <c r="D90" s="21"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
@@ -1750,7 +1850,7 @@
       <c r="A91" s="8"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
+      <c r="D91" s="21"/>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
@@ -1760,7 +1860,7 @@
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
+      <c r="D92" s="21"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7"/>
       <c r="G92" s="7"/>
@@ -1770,7 +1870,7 @@
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
+      <c r="D93" s="21"/>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
@@ -1780,7 +1880,7 @@
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
+      <c r="D94" s="21"/>
       <c r="E94" s="7"/>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
@@ -1790,7 +1890,7 @@
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
+      <c r="D95" s="21"/>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
@@ -1800,7 +1900,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
+      <c r="D96" s="21"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
@@ -1810,7 +1910,7 @@
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
+      <c r="D97" s="21"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
@@ -1820,7 +1920,7 @@
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
+      <c r="D98" s="21"/>
       <c r="E98" s="7"/>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
@@ -1830,7 +1930,7 @@
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
+      <c r="D99" s="21"/>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
@@ -1840,7 +1940,7 @@
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
+      <c r="D100" s="21"/>
       <c r="E100" s="7"/>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
@@ -1850,7 +1950,7 @@
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
+      <c r="D101" s="21"/>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
@@ -1860,7 +1960,7 @@
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
+      <c r="D102" s="21"/>
       <c r="E102" s="7"/>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
@@ -1870,7 +1970,7 @@
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
+      <c r="D103" s="21"/>
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
@@ -1880,7 +1980,7 @@
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
+      <c r="D104" s="21"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
@@ -1890,7 +1990,7 @@
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
+      <c r="D105" s="21"/>
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
@@ -1900,7 +2000,7 @@
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
+      <c r="D106" s="21"/>
       <c r="E106" s="7"/>
       <c r="F106" s="7"/>
       <c r="G106" s="7"/>
@@ -1910,7 +2010,7 @@
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
+      <c r="D107" s="21"/>
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
@@ -1920,7 +2020,7 @@
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
+      <c r="D108" s="21"/>
       <c r="E108" s="7"/>
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
@@ -1930,7 +2030,7 @@
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
+      <c r="D109" s="21"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
@@ -1940,7 +2040,7 @@
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
+      <c r="D110" s="21"/>
       <c r="E110" s="7"/>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
@@ -1950,7 +2050,7 @@
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
+      <c r="D111" s="21"/>
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
@@ -1960,7 +2060,7 @@
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
+      <c r="D112" s="21"/>
       <c r="E112" s="7"/>
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
@@ -1970,7 +2070,7 @@
       <c r="A113" s="8"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
+      <c r="D113" s="21"/>
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
@@ -1980,7 +2080,7 @@
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
+      <c r="D114" s="21"/>
       <c r="E114" s="7"/>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -1990,7 +2090,7 @@
       <c r="A115" s="8"/>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
+      <c r="D115" s="21"/>
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
       <c r="G115" s="8"/>
@@ -2000,7 +2100,7 @@
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
+      <c r="D116" s="21"/>
       <c r="E116" s="7"/>
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
@@ -2010,7 +2110,7 @@
       <c r="A117" s="8"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
+      <c r="D117" s="21"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
@@ -2020,7 +2120,7 @@
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
+      <c r="D118" s="21"/>
       <c r="E118" s="7"/>
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
@@ -2030,7 +2130,7 @@
       <c r="A119" s="8"/>
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
+      <c r="D119" s="21"/>
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
       <c r="G119" s="8"/>
@@ -2040,7 +2140,7 @@
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
+      <c r="D120" s="21"/>
       <c r="E120" s="7"/>
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
@@ -2050,7 +2150,7 @@
       <c r="A121" s="8"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
+      <c r="D121" s="21"/>
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
       <c r="G121" s="8"/>
@@ -2060,7 +2160,7 @@
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
+      <c r="D122" s="21"/>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
       <c r="G122" s="7"/>
@@ -2070,7 +2170,7 @@
       <c r="A123" s="8"/>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
+      <c r="D123" s="21"/>
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
       <c r="G123" s="8"/>
@@ -2080,7 +2180,7 @@
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
+      <c r="D124" s="21"/>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
       <c r="G124" s="7"/>
@@ -2090,7 +2190,7 @@
       <c r="A125" s="8"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
+      <c r="D125" s="21"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
@@ -2100,7 +2200,7 @@
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
+      <c r="D126" s="21"/>
       <c r="E126" s="7"/>
       <c r="F126" s="7"/>
       <c r="G126" s="7"/>
@@ -2110,7 +2210,7 @@
       <c r="A127" s="8"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
+      <c r="D127" s="21"/>
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
       <c r="G127" s="8"/>
@@ -2120,7 +2220,7 @@
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
+      <c r="D128" s="21"/>
       <c r="E128" s="7"/>
       <c r="F128" s="7"/>
       <c r="G128" s="7"/>
@@ -2130,7 +2230,7 @@
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
+      <c r="D129" s="21"/>
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
       <c r="G129" s="8"/>
@@ -2140,7 +2240,7 @@
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
+      <c r="D130" s="21"/>
       <c r="E130" s="7"/>
       <c r="F130" s="7"/>
       <c r="G130" s="7"/>
@@ -2150,7 +2250,7 @@
       <c r="A131" s="8"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
+      <c r="D131" s="21"/>
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
       <c r="G131" s="8"/>
@@ -2160,7 +2260,7 @@
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
+      <c r="D132" s="21"/>
       <c r="E132" s="7"/>
       <c r="F132" s="7"/>
       <c r="G132" s="7"/>
@@ -2170,7 +2270,7 @@
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
+      <c r="D133" s="21"/>
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
       <c r="G133" s="8"/>
@@ -2180,7 +2280,7 @@
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
+      <c r="D134" s="21"/>
       <c r="E134" s="7"/>
       <c r="F134" s="7"/>
       <c r="G134" s="7"/>
@@ -2190,7 +2290,7 @@
       <c r="A135" s="8"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
+      <c r="D135" s="21"/>
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
@@ -2200,7 +2300,7 @@
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
+      <c r="D136" s="21"/>
       <c r="E136" s="7"/>
       <c r="F136" s="7"/>
       <c r="G136" s="7"/>
@@ -2210,7 +2310,7 @@
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
+      <c r="D137" s="21"/>
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
@@ -2220,7 +2320,7 @@
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
+      <c r="D138" s="21"/>
       <c r="E138" s="7"/>
       <c r="F138" s="7"/>
       <c r="G138" s="7"/>
@@ -2230,7 +2330,7 @@
       <c r="A139" s="8"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
+      <c r="D139" s="21"/>
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
@@ -2240,7 +2340,7 @@
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
+      <c r="D140" s="21"/>
       <c r="E140" s="7"/>
       <c r="F140" s="7"/>
       <c r="G140" s="7"/>
@@ -2250,7 +2350,7 @@
       <c r="A141" s="8"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
+      <c r="D141" s="21"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
@@ -2260,7 +2360,7 @@
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
+      <c r="D142" s="21"/>
       <c r="E142" s="7"/>
       <c r="F142" s="7"/>
       <c r="G142" s="7"/>
@@ -2270,7 +2370,7 @@
       <c r="A143" s="8"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
+      <c r="D143" s="21"/>
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
       <c r="G143" s="8"/>
@@ -2280,7 +2380,7 @@
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
+      <c r="D144" s="21"/>
       <c r="E144" s="7"/>
       <c r="F144" s="7"/>
       <c r="G144" s="7"/>
@@ -2290,7 +2390,7 @@
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
+      <c r="D145" s="21"/>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
       <c r="G145" s="8"/>
@@ -2300,7 +2400,7 @@
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
+      <c r="D146" s="21"/>
       <c r="E146" s="7"/>
       <c r="F146" s="7"/>
       <c r="G146" s="7"/>
@@ -2310,7 +2410,7 @@
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
+      <c r="D147" s="21"/>
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
       <c r="G147" s="8"/>
@@ -2320,7 +2420,7 @@
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
+      <c r="D148" s="21"/>
       <c r="E148" s="7"/>
       <c r="F148" s="7"/>
       <c r="G148" s="7"/>
@@ -2330,7 +2430,7 @@
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
+      <c r="D149" s="21"/>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
       <c r="G149" s="8"/>
@@ -2340,7 +2440,7 @@
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
+      <c r="D150" s="21"/>
       <c r="E150" s="7"/>
       <c r="F150" s="7"/>
       <c r="G150" s="7"/>
@@ -2350,7 +2450,7 @@
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
+      <c r="D151" s="21"/>
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
       <c r="G151" s="8"/>
@@ -2360,7 +2460,7 @@
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
+      <c r="D152" s="21"/>
       <c r="E152" s="7"/>
       <c r="F152" s="7"/>
       <c r="G152" s="7"/>
@@ -2370,7 +2470,7 @@
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
+      <c r="D153" s="21"/>
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
       <c r="G153" s="8"/>
@@ -2380,7 +2480,7 @@
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
+      <c r="D154" s="21"/>
       <c r="E154" s="7"/>
       <c r="F154" s="7"/>
       <c r="G154" s="7"/>
@@ -2390,7 +2490,7 @@
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
+      <c r="D155" s="21"/>
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
       <c r="G155" s="8"/>
@@ -2400,7 +2500,7 @@
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
+      <c r="D156" s="21"/>
       <c r="E156" s="7"/>
       <c r="F156" s="7"/>
       <c r="G156" s="7"/>
@@ -2410,7 +2510,7 @@
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
+      <c r="D157" s="21"/>
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
       <c r="G157" s="8"/>
@@ -2420,7 +2520,7 @@
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
+      <c r="D158" s="21"/>
       <c r="E158" s="7"/>
       <c r="F158" s="7"/>
       <c r="G158" s="7"/>
@@ -2430,7 +2530,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
+      <c r="D159" s="21"/>
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
       <c r="G159" s="8"/>
@@ -2440,7 +2540,7 @@
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
+      <c r="D160" s="21"/>
       <c r="E160" s="7"/>
       <c r="F160" s="7"/>
       <c r="G160" s="7"/>
@@ -2450,7 +2550,7 @@
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
+      <c r="D161" s="21"/>
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
@@ -2460,7 +2560,7 @@
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
+      <c r="D162" s="21"/>
       <c r="E162" s="7"/>
       <c r="F162" s="7"/>
       <c r="G162" s="7"/>
@@ -2470,7 +2570,7 @@
       <c r="A163" s="8"/>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
+      <c r="D163" s="21"/>
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
       <c r="G163" s="8"/>
@@ -2480,7 +2580,7 @@
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
-      <c r="D164" s="7"/>
+      <c r="D164" s="21"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7"/>
       <c r="G164" s="7"/>
@@ -2490,7 +2590,7 @@
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
+      <c r="D165" s="21"/>
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
       <c r="G165" s="8"/>
@@ -2500,7 +2600,7 @@
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
+      <c r="D166" s="21"/>
       <c r="E166" s="7"/>
       <c r="F166" s="7"/>
       <c r="G166" s="7"/>
@@ -2510,7 +2610,7 @@
       <c r="A167" s="8"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
+      <c r="D167" s="21"/>
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
       <c r="G167" s="8"/>
@@ -2520,7 +2620,7 @@
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
+      <c r="D168" s="21"/>
       <c r="E168" s="7"/>
       <c r="F168" s="7"/>
       <c r="G168" s="7"/>
@@ -2530,7 +2630,7 @@
       <c r="A169" s="8"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
+      <c r="D169" s="21"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
       <c r="G169" s="8"/>
@@ -2540,7 +2640,7 @@
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
+      <c r="D170" s="21"/>
       <c r="E170" s="7"/>
       <c r="F170" s="7"/>
       <c r="G170" s="7"/>
@@ -2550,7 +2650,7 @@
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
+      <c r="D171" s="21"/>
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
       <c r="G171" s="8"/>
@@ -2560,7 +2660,7 @@
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
-      <c r="D172" s="7"/>
+      <c r="D172" s="21"/>
       <c r="E172" s="7"/>
       <c r="F172" s="7"/>
       <c r="G172" s="7"/>
@@ -2570,7 +2670,7 @@
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
+      <c r="D173" s="21"/>
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
       <c r="G173" s="8"/>
@@ -2580,7 +2680,7 @@
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
-      <c r="D174" s="7"/>
+      <c r="D174" s="21"/>
       <c r="E174" s="7"/>
       <c r="F174" s="7"/>
       <c r="G174" s="7"/>
@@ -2590,7 +2690,7 @@
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
+      <c r="D175" s="21"/>
       <c r="E175" s="8"/>
       <c r="F175" s="8"/>
       <c r="G175" s="8"/>
@@ -2600,7 +2700,7 @@
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
-      <c r="D176" s="7"/>
+      <c r="D176" s="21"/>
       <c r="E176" s="7"/>
       <c r="F176" s="7"/>
       <c r="G176" s="7"/>
@@ -2610,7 +2710,7 @@
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
+      <c r="D177" s="21"/>
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
       <c r="G177" s="8"/>
@@ -2620,7 +2720,7 @@
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
-      <c r="D178" s="7"/>
+      <c r="D178" s="21"/>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
       <c r="G178" s="7"/>
@@ -2630,7 +2730,7 @@
       <c r="A179" s="8"/>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
+      <c r="D179" s="21"/>
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
       <c r="G179" s="8"/>
@@ -2640,7 +2740,7 @@
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
-      <c r="D180" s="7"/>
+      <c r="D180" s="21"/>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
       <c r="G180" s="7"/>
@@ -2650,7 +2750,7 @@
       <c r="A181" s="8"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
+      <c r="D181" s="21"/>
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
       <c r="G181" s="8"/>
@@ -2660,7 +2760,7 @@
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
-      <c r="D182" s="7"/>
+      <c r="D182" s="21"/>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
       <c r="G182" s="7"/>
@@ -2670,7 +2770,7 @@
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
+      <c r="D183" s="21"/>
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
       <c r="G183" s="8"/>
@@ -2680,7 +2780,7 @@
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
-      <c r="D184" s="7"/>
+      <c r="D184" s="21"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
       <c r="G184" s="7"/>
@@ -2690,7 +2790,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
+      <c r="D185" s="21"/>
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
       <c r="G185" s="8"/>
@@ -2700,7 +2800,7 @@
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
-      <c r="D186" s="7"/>
+      <c r="D186" s="21"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
       <c r="G186" s="7"/>
@@ -2710,7 +2810,7 @@
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
+      <c r="D187" s="21"/>
       <c r="E187" s="8"/>
       <c r="F187" s="8"/>
       <c r="G187" s="8"/>
@@ -2720,7 +2820,7 @@
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
-      <c r="D188" s="7"/>
+      <c r="D188" s="21"/>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
       <c r="G188" s="7"/>
@@ -2730,7 +2830,7 @@
       <c r="A189" s="8"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
+      <c r="D189" s="21"/>
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
       <c r="G189" s="8"/>
@@ -2740,7 +2840,7 @@
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
-      <c r="D190" s="7"/>
+      <c r="D190" s="21"/>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
       <c r="G190" s="7"/>
@@ -2750,7 +2850,7 @@
       <c r="A191" s="8"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
+      <c r="D191" s="21"/>
       <c r="E191" s="8"/>
       <c r="F191" s="8"/>
       <c r="G191" s="8"/>
@@ -2760,7 +2860,7 @@
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
-      <c r="D192" s="7"/>
+      <c r="D192" s="21"/>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
       <c r="G192" s="7"/>
@@ -2770,7 +2870,7 @@
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
+      <c r="D193" s="21"/>
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
       <c r="G193" s="8"/>
@@ -2780,7 +2880,7 @@
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
-      <c r="D194" s="7"/>
+      <c r="D194" s="21"/>
       <c r="E194" s="7"/>
       <c r="F194" s="7"/>
       <c r="G194" s="7"/>
@@ -2790,7 +2890,7 @@
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
+      <c r="D195" s="21"/>
       <c r="E195" s="8"/>
       <c r="F195" s="8"/>
       <c r="G195" s="8"/>
@@ -2800,7 +2900,7 @@
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
-      <c r="D196" s="7"/>
+      <c r="D196" s="21"/>
       <c r="E196" s="7"/>
       <c r="F196" s="7"/>
       <c r="G196" s="7"/>
@@ -2810,7 +2910,7 @@
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
+      <c r="D197" s="21"/>
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
       <c r="G197" s="8"/>
@@ -2820,7 +2920,7 @@
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
-      <c r="D198" s="7"/>
+      <c r="D198" s="21"/>
       <c r="E198" s="7"/>
       <c r="F198" s="7"/>
       <c r="G198" s="7"/>
@@ -2830,7 +2930,7 @@
       <c r="A199" s="8"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
+      <c r="D199" s="21"/>
       <c r="E199" s="8"/>
       <c r="F199" s="8"/>
       <c r="G199" s="8"/>
@@ -2840,7 +2940,7 @@
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
-      <c r="D200" s="7"/>
+      <c r="D200" s="21"/>
       <c r="E200" s="7"/>
       <c r="F200" s="7"/>
       <c r="G200" s="7"/>
@@ -2850,7 +2950,7 @@
       <c r="A201" s="8"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
-      <c r="D201" s="8"/>
+      <c r="D201" s="21"/>
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
       <c r="G201" s="8"/>
@@ -2877,67 +2977,67 @@
   <dimension ref="A1:O201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="35" customWidth="1"/>
+    <col min="5" max="5" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="48.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="40" customWidth="1"/>
-    <col min="14" max="14" width="25" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" style="22" customWidth="1"/>
+    <col min="11" max="11" width="12" style="22" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="22" customWidth="1"/>
+    <col min="13" max="13" width="40" style="22" customWidth="1"/>
+    <col min="14" max="14" width="25" style="22" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>46</v>
+      <c r="F1" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="G1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>19</v>
+      <c r="N1" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -2945,16 +3045,16 @@
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="14"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
       <c r="O2" s="7"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -2962,16 +3062,16 @@
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
       <c r="O3" s="8"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -2979,135 +3079,135 @@
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
       <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="12"/>
       <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="14"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
       <c r="O6" s="7"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="15"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
       <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="14"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
       <c r="O8" s="7"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="15"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
       <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="14"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
       <c r="O10" s="7"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="15"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
       <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -3116,15 +3216,15 @@
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="F12" s="14"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -3133,15 +3233,15 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
       <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -3150,15 +3250,15 @@
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="F14" s="14"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -3167,15 +3267,15 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="F15" s="15"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
       <c r="O15" s="8"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -3184,15 +3284,15 @@
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="F16" s="14"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
       <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -3201,15 +3301,15 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
       <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -3218,15 +3318,15 @@
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="F18" s="14"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
       <c r="O18" s="7"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -3235,15 +3335,15 @@
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="F19" s="15"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
       <c r="O19" s="8"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -3252,15 +3352,15 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="F20" s="14"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -3269,15 +3369,15 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
       <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -3286,15 +3386,15 @@
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="F22" s="14"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
       <c r="O22" s="7"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -3303,15 +3403,15 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="F23" s="15"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
       <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3320,15 +3420,15 @@
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="F24" s="14"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
       <c r="O24" s="7"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -3337,15 +3437,15 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="F25" s="15"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
       <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3354,15 +3454,15 @@
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="F26" s="14"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
       <c r="O26" s="7"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -3371,15 +3471,15 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
+      <c r="F27" s="15"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
       <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -3388,15 +3488,15 @@
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="F28" s="14"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
       <c r="O28" s="7"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3405,15 +3505,15 @@
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="F29" s="15"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
       <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3422,15 +3522,15 @@
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="F30" s="14"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -3439,15 +3539,15 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="F31" s="15"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
       <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -3456,15 +3556,15 @@
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+      <c r="F32" s="14"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
       <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -3473,15 +3573,15 @@
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="F33" s="15"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
       <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -3490,15 +3590,15 @@
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
+      <c r="F34" s="14"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="21"/>
       <c r="O34" s="7"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -3507,15 +3607,15 @@
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
+      <c r="F35" s="15"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
       <c r="O35" s="8"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3524,15 +3624,15 @@
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="F36" s="14"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
       <c r="O36" s="7"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -3541,15 +3641,15 @@
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
+      <c r="F37" s="15"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
       <c r="O37" s="8"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -3558,15 +3658,15 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
+      <c r="F38" s="14"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21"/>
       <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -3575,15 +3675,15 @@
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="F39" s="15"/>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="21"/>
       <c r="O39" s="8"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -3592,15 +3692,15 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
+      <c r="F40" s="14"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="21"/>
       <c r="O40" s="7"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -3609,15 +3709,15 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
+      <c r="F41" s="15"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="21"/>
+      <c r="N41" s="21"/>
       <c r="O41" s="8"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -3626,15 +3726,15 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
+      <c r="F42" s="14"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="21"/>
       <c r="O42" s="7"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -3643,15 +3743,15 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="F43" s="15"/>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21"/>
       <c r="O43" s="8"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -3660,15 +3760,15 @@
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+      <c r="F44" s="14"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="21"/>
       <c r="O44" s="7"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -3677,15 +3777,15 @@
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
+      <c r="F45" s="15"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="21"/>
+      <c r="N45" s="21"/>
       <c r="O45" s="8"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -3694,15 +3794,15 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
+      <c r="F46" s="14"/>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="21"/>
       <c r="O46" s="7"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -3711,15 +3811,15 @@
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
+      <c r="F47" s="15"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="21"/>
       <c r="O47" s="8"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -3728,15 +3828,15 @@
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
+      <c r="F48" s="14"/>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
+      <c r="J48" s="21"/>
+      <c r="K48" s="21"/>
+      <c r="L48" s="21"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="21"/>
       <c r="O48" s="7"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -3745,15 +3845,15 @@
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
+      <c r="F49" s="15"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="21"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
       <c r="O49" s="8"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -3762,15 +3862,15 @@
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
+      <c r="F50" s="14"/>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="21"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21"/>
       <c r="O50" s="7"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -3779,15 +3879,15 @@
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
+      <c r="F51" s="15"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="21"/>
       <c r="O51" s="8"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -3796,15 +3896,15 @@
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
+      <c r="F52" s="14"/>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="21"/>
       <c r="O52" s="7"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -3813,15 +3913,15 @@
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
+      <c r="F53" s="15"/>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="8"/>
-      <c r="N53" s="8"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="21"/>
       <c r="O53" s="8"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -3830,15 +3930,15 @@
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
+      <c r="F54" s="14"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
       <c r="O54" s="7"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -3847,15 +3947,15 @@
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
+      <c r="F55" s="15"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="8"/>
-      <c r="N55" s="8"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
       <c r="O55" s="8"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -3864,15 +3964,15 @@
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
+      <c r="F56" s="14"/>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
-      <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
-      <c r="M56" s="7"/>
-      <c r="N56" s="7"/>
+      <c r="J56" s="21"/>
+      <c r="K56" s="21"/>
+      <c r="L56" s="21"/>
+      <c r="M56" s="21"/>
+      <c r="N56" s="21"/>
       <c r="O56" s="7"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -3881,15 +3981,15 @@
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
+      <c r="F57" s="15"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="8"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="21"/>
+      <c r="L57" s="21"/>
+      <c r="M57" s="21"/>
+      <c r="N57" s="21"/>
       <c r="O57" s="8"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
@@ -3898,15 +3998,15 @@
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
+      <c r="F58" s="14"/>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
-      <c r="N58" s="7"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="21"/>
+      <c r="L58" s="21"/>
+      <c r="M58" s="21"/>
+      <c r="N58" s="21"/>
       <c r="O58" s="7"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -3915,15 +4015,15 @@
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
+      <c r="F59" s="15"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="8"/>
-      <c r="N59" s="8"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="21"/>
+      <c r="M59" s="21"/>
+      <c r="N59" s="21"/>
       <c r="O59" s="8"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -3932,15 +4032,15 @@
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
+      <c r="F60" s="14"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
-      <c r="N60" s="7"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="21"/>
+      <c r="M60" s="21"/>
+      <c r="N60" s="21"/>
       <c r="O60" s="7"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -3949,15 +4049,15 @@
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
+      <c r="F61" s="15"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
-      <c r="N61" s="8"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="21"/>
+      <c r="L61" s="21"/>
+      <c r="M61" s="21"/>
+      <c r="N61" s="21"/>
       <c r="O61" s="8"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -3966,15 +4066,15 @@
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
+      <c r="F62" s="14"/>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="7"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="21"/>
+      <c r="L62" s="21"/>
+      <c r="M62" s="21"/>
+      <c r="N62" s="21"/>
       <c r="O62" s="7"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -3983,15 +4083,15 @@
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
+      <c r="F63" s="15"/>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="8"/>
-      <c r="N63" s="8"/>
+      <c r="J63" s="21"/>
+      <c r="K63" s="21"/>
+      <c r="L63" s="21"/>
+      <c r="M63" s="21"/>
+      <c r="N63" s="21"/>
       <c r="O63" s="8"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -4000,15 +4100,15 @@
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
+      <c r="F64" s="14"/>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="7"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="21"/>
+      <c r="L64" s="21"/>
+      <c r="M64" s="21"/>
+      <c r="N64" s="21"/>
       <c r="O64" s="7"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -4017,15 +4117,15 @@
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
+      <c r="F65" s="15"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="8"/>
-      <c r="N65" s="8"/>
+      <c r="J65" s="21"/>
+      <c r="K65" s="21"/>
+      <c r="L65" s="21"/>
+      <c r="M65" s="21"/>
+      <c r="N65" s="21"/>
       <c r="O65" s="8"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
@@ -4034,15 +4134,15 @@
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
+      <c r="F66" s="14"/>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
-      <c r="J66" s="7"/>
-      <c r="K66" s="7"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
-      <c r="N66" s="7"/>
+      <c r="J66" s="21"/>
+      <c r="K66" s="21"/>
+      <c r="L66" s="21"/>
+      <c r="M66" s="21"/>
+      <c r="N66" s="21"/>
       <c r="O66" s="7"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
@@ -4051,15 +4151,15 @@
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
+      <c r="F67" s="15"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
-      <c r="M67" s="8"/>
-      <c r="N67" s="8"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="21"/>
+      <c r="L67" s="21"/>
+      <c r="M67" s="21"/>
+      <c r="N67" s="21"/>
       <c r="O67" s="8"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
@@ -4068,15 +4168,15 @@
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
+      <c r="F68" s="14"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="7"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
       <c r="O68" s="7"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
@@ -4085,15 +4185,15 @@
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
+      <c r="F69" s="15"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
       <c r="O69" s="8"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
@@ -4102,15 +4202,15 @@
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
+      <c r="F70" s="14"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="7"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="21"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
       <c r="O70" s="7"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
@@ -4119,15 +4219,15 @@
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
+      <c r="F71" s="15"/>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
       <c r="O71" s="8"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
@@ -4136,15 +4236,15 @@
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
+      <c r="F72" s="14"/>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
-      <c r="K72" s="7"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="7"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
       <c r="O72" s="7"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
@@ -4153,15 +4253,15 @@
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
+      <c r="F73" s="15"/>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
       <c r="O73" s="8"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
@@ -4170,15 +4270,15 @@
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
+      <c r="F74" s="14"/>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="21"/>
+      <c r="L74" s="21"/>
+      <c r="M74" s="21"/>
+      <c r="N74" s="21"/>
       <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
@@ -4187,15 +4287,15 @@
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
+      <c r="F75" s="15"/>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
       <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8"/>
-      <c r="N75" s="8"/>
+      <c r="J75" s="21"/>
+      <c r="K75" s="21"/>
+      <c r="L75" s="21"/>
+      <c r="M75" s="21"/>
+      <c r="N75" s="21"/>
       <c r="O75" s="8"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
@@ -4204,15 +4304,15 @@
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
+      <c r="F76" s="14"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="7"/>
+      <c r="J76" s="21"/>
+      <c r="K76" s="21"/>
+      <c r="L76" s="21"/>
+      <c r="M76" s="21"/>
+      <c r="N76" s="21"/>
       <c r="O76" s="7"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
@@ -4221,15 +4321,15 @@
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
+      <c r="F77" s="15"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
-      <c r="N77" s="8"/>
+      <c r="J77" s="21"/>
+      <c r="K77" s="21"/>
+      <c r="L77" s="21"/>
+      <c r="M77" s="21"/>
+      <c r="N77" s="21"/>
       <c r="O77" s="8"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
@@ -4238,15 +4338,15 @@
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
+      <c r="F78" s="14"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
-      <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
-      <c r="N78" s="7"/>
+      <c r="J78" s="21"/>
+      <c r="K78" s="21"/>
+      <c r="L78" s="21"/>
+      <c r="M78" s="21"/>
+      <c r="N78" s="21"/>
       <c r="O78" s="7"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
@@ -4255,15 +4355,15 @@
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
+      <c r="F79" s="15"/>
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
       <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8"/>
-      <c r="N79" s="8"/>
+      <c r="J79" s="21"/>
+      <c r="K79" s="21"/>
+      <c r="L79" s="21"/>
+      <c r="M79" s="21"/>
+      <c r="N79" s="21"/>
       <c r="O79" s="8"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
@@ -4272,15 +4372,15 @@
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
+      <c r="F80" s="14"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
+      <c r="J80" s="21"/>
+      <c r="K80" s="21"/>
+      <c r="L80" s="21"/>
+      <c r="M80" s="21"/>
+      <c r="N80" s="21"/>
       <c r="O80" s="7"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
@@ -4289,15 +4389,15 @@
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
+      <c r="F81" s="15"/>
       <c r="G81" s="8"/>
       <c r="H81" s="8"/>
       <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-      <c r="N81" s="8"/>
+      <c r="J81" s="21"/>
+      <c r="K81" s="21"/>
+      <c r="L81" s="21"/>
+      <c r="M81" s="21"/>
+      <c r="N81" s="21"/>
       <c r="O81" s="8"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
@@ -4306,15 +4406,15 @@
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
+      <c r="F82" s="14"/>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
-      <c r="K82" s="7"/>
-      <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
-      <c r="N82" s="7"/>
+      <c r="J82" s="21"/>
+      <c r="K82" s="21"/>
+      <c r="L82" s="21"/>
+      <c r="M82" s="21"/>
+      <c r="N82" s="21"/>
       <c r="O82" s="7"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
@@ -4323,15 +4423,15 @@
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
+      <c r="F83" s="15"/>
       <c r="G83" s="8"/>
       <c r="H83" s="8"/>
       <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-      <c r="N83" s="8"/>
+      <c r="J83" s="21"/>
+      <c r="K83" s="21"/>
+      <c r="L83" s="21"/>
+      <c r="M83" s="21"/>
+      <c r="N83" s="21"/>
       <c r="O83" s="8"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
@@ -4340,15 +4440,15 @@
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
+      <c r="F84" s="14"/>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
-      <c r="J84" s="7"/>
-      <c r="K84" s="7"/>
-      <c r="L84" s="7"/>
-      <c r="M84" s="7"/>
-      <c r="N84" s="7"/>
+      <c r="J84" s="21"/>
+      <c r="K84" s="21"/>
+      <c r="L84" s="21"/>
+      <c r="M84" s="21"/>
+      <c r="N84" s="21"/>
       <c r="O84" s="7"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
@@ -4357,15 +4457,15 @@
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
+      <c r="F85" s="15"/>
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
       <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-      <c r="N85" s="8"/>
+      <c r="J85" s="21"/>
+      <c r="K85" s="21"/>
+      <c r="L85" s="21"/>
+      <c r="M85" s="21"/>
+      <c r="N85" s="21"/>
       <c r="O85" s="8"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
@@ -4374,15 +4474,15 @@
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
+      <c r="F86" s="14"/>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="7"/>
-      <c r="J86" s="7"/>
-      <c r="K86" s="7"/>
-      <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
-      <c r="N86" s="7"/>
+      <c r="J86" s="21"/>
+      <c r="K86" s="21"/>
+      <c r="L86" s="21"/>
+      <c r="M86" s="21"/>
+      <c r="N86" s="21"/>
       <c r="O86" s="7"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
@@ -4391,15 +4491,15 @@
       <c r="C87" s="8"/>
       <c r="D87" s="8"/>
       <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
+      <c r="F87" s="15"/>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8"/>
-      <c r="N87" s="8"/>
+      <c r="J87" s="21"/>
+      <c r="K87" s="21"/>
+      <c r="L87" s="21"/>
+      <c r="M87" s="21"/>
+      <c r="N87" s="21"/>
       <c r="O87" s="8"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
@@ -4408,15 +4508,15 @@
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
+      <c r="F88" s="14"/>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="7"/>
-      <c r="J88" s="7"/>
-      <c r="K88" s="7"/>
-      <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
-      <c r="N88" s="7"/>
+      <c r="J88" s="21"/>
+      <c r="K88" s="21"/>
+      <c r="L88" s="21"/>
+      <c r="M88" s="21"/>
+      <c r="N88" s="21"/>
       <c r="O88" s="7"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
@@ -4425,15 +4525,15 @@
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
+      <c r="F89" s="15"/>
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
       <c r="I89" s="8"/>
-      <c r="J89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
-      <c r="M89" s="8"/>
-      <c r="N89" s="8"/>
+      <c r="J89" s="21"/>
+      <c r="K89" s="21"/>
+      <c r="L89" s="21"/>
+      <c r="M89" s="21"/>
+      <c r="N89" s="21"/>
       <c r="O89" s="8"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
@@ -4442,15 +4542,15 @@
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
+      <c r="F90" s="14"/>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
-      <c r="J90" s="7"/>
-      <c r="K90" s="7"/>
-      <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
-      <c r="N90" s="7"/>
+      <c r="J90" s="21"/>
+      <c r="K90" s="21"/>
+      <c r="L90" s="21"/>
+      <c r="M90" s="21"/>
+      <c r="N90" s="21"/>
       <c r="O90" s="7"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
@@ -4459,15 +4559,15 @@
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
       <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
+      <c r="F91" s="15"/>
       <c r="G91" s="8"/>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="M91" s="8"/>
-      <c r="N91" s="8"/>
+      <c r="J91" s="21"/>
+      <c r="K91" s="21"/>
+      <c r="L91" s="21"/>
+      <c r="M91" s="21"/>
+      <c r="N91" s="21"/>
       <c r="O91" s="8"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
@@ -4476,15 +4576,15 @@
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
+      <c r="F92" s="14"/>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
-      <c r="J92" s="7"/>
-      <c r="K92" s="7"/>
-      <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
-      <c r="N92" s="7"/>
+      <c r="J92" s="21"/>
+      <c r="K92" s="21"/>
+      <c r="L92" s="21"/>
+      <c r="M92" s="21"/>
+      <c r="N92" s="21"/>
       <c r="O92" s="7"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
@@ -4493,15 +4593,15 @@
       <c r="C93" s="8"/>
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
+      <c r="F93" s="15"/>
       <c r="G93" s="8"/>
       <c r="H93" s="8"/>
       <c r="I93" s="8"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
-      <c r="M93" s="8"/>
-      <c r="N93" s="8"/>
+      <c r="J93" s="21"/>
+      <c r="K93" s="21"/>
+      <c r="L93" s="21"/>
+      <c r="M93" s="21"/>
+      <c r="N93" s="21"/>
       <c r="O93" s="8"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
@@ -4510,15 +4610,15 @@
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
+      <c r="F94" s="14"/>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
-      <c r="J94" s="7"/>
-      <c r="K94" s="7"/>
-      <c r="L94" s="7"/>
-      <c r="M94" s="7"/>
-      <c r="N94" s="7"/>
+      <c r="J94" s="21"/>
+      <c r="K94" s="21"/>
+      <c r="L94" s="21"/>
+      <c r="M94" s="21"/>
+      <c r="N94" s="21"/>
       <c r="O94" s="7"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
@@ -4527,15 +4627,15 @@
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
+      <c r="F95" s="15"/>
       <c r="G95" s="8"/>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="M95" s="8"/>
-      <c r="N95" s="8"/>
+      <c r="J95" s="21"/>
+      <c r="K95" s="21"/>
+      <c r="L95" s="21"/>
+      <c r="M95" s="21"/>
+      <c r="N95" s="21"/>
       <c r="O95" s="8"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
@@ -4544,15 +4644,15 @@
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
+      <c r="F96" s="14"/>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
-      <c r="J96" s="7"/>
-      <c r="K96" s="7"/>
-      <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
-      <c r="N96" s="7"/>
+      <c r="J96" s="21"/>
+      <c r="K96" s="21"/>
+      <c r="L96" s="21"/>
+      <c r="M96" s="21"/>
+      <c r="N96" s="21"/>
       <c r="O96" s="7"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
@@ -4561,15 +4661,15 @@
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
+      <c r="F97" s="15"/>
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="M97" s="8"/>
-      <c r="N97" s="8"/>
+      <c r="J97" s="21"/>
+      <c r="K97" s="21"/>
+      <c r="L97" s="21"/>
+      <c r="M97" s="21"/>
+      <c r="N97" s="21"/>
       <c r="O97" s="8"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
@@ -4578,15 +4678,15 @@
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
+      <c r="F98" s="14"/>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
-      <c r="J98" s="7"/>
-      <c r="K98" s="7"/>
-      <c r="L98" s="7"/>
-      <c r="M98" s="7"/>
-      <c r="N98" s="7"/>
+      <c r="J98" s="21"/>
+      <c r="K98" s="21"/>
+      <c r="L98" s="21"/>
+      <c r="M98" s="21"/>
+      <c r="N98" s="21"/>
       <c r="O98" s="7"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
@@ -4595,15 +4695,15 @@
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
       <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
+      <c r="F99" s="15"/>
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="8"/>
-      <c r="N99" s="8"/>
+      <c r="J99" s="21"/>
+      <c r="K99" s="21"/>
+      <c r="L99" s="21"/>
+      <c r="M99" s="21"/>
+      <c r="N99" s="21"/>
       <c r="O99" s="8"/>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
@@ -4612,15 +4712,15 @@
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
+      <c r="F100" s="14"/>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="7"/>
-      <c r="J100" s="7"/>
-      <c r="K100" s="7"/>
-      <c r="L100" s="7"/>
-      <c r="M100" s="7"/>
-      <c r="N100" s="7"/>
+      <c r="J100" s="21"/>
+      <c r="K100" s="21"/>
+      <c r="L100" s="21"/>
+      <c r="M100" s="21"/>
+      <c r="N100" s="21"/>
       <c r="O100" s="7"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
@@ -4629,15 +4729,15 @@
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
+      <c r="F101" s="15"/>
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
-      <c r="M101" s="8"/>
-      <c r="N101" s="8"/>
+      <c r="J101" s="21"/>
+      <c r="K101" s="21"/>
+      <c r="L101" s="21"/>
+      <c r="M101" s="21"/>
+      <c r="N101" s="21"/>
       <c r="O101" s="8"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
@@ -4646,15 +4746,15 @@
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
+      <c r="F102" s="14"/>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
-      <c r="J102" s="7"/>
-      <c r="K102" s="7"/>
-      <c r="L102" s="7"/>
-      <c r="M102" s="7"/>
-      <c r="N102" s="7"/>
+      <c r="J102" s="21"/>
+      <c r="K102" s="21"/>
+      <c r="L102" s="21"/>
+      <c r="M102" s="21"/>
+      <c r="N102" s="21"/>
       <c r="O102" s="7"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
@@ -4663,15 +4763,15 @@
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
+      <c r="F103" s="15"/>
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
-      <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
-      <c r="M103" s="8"/>
-      <c r="N103" s="8"/>
+      <c r="J103" s="21"/>
+      <c r="K103" s="21"/>
+      <c r="L103" s="21"/>
+      <c r="M103" s="21"/>
+      <c r="N103" s="21"/>
       <c r="O103" s="8"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
@@ -4680,15 +4780,15 @@
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
+      <c r="F104" s="14"/>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
-      <c r="J104" s="7"/>
-      <c r="K104" s="7"/>
-      <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
-      <c r="N104" s="7"/>
+      <c r="J104" s="21"/>
+      <c r="K104" s="21"/>
+      <c r="L104" s="21"/>
+      <c r="M104" s="21"/>
+      <c r="N104" s="21"/>
       <c r="O104" s="7"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
@@ -4697,15 +4797,15 @@
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
+      <c r="F105" s="15"/>
       <c r="G105" s="8"/>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
-      <c r="J105" s="8"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="8"/>
-      <c r="M105" s="8"/>
-      <c r="N105" s="8"/>
+      <c r="J105" s="21"/>
+      <c r="K105" s="21"/>
+      <c r="L105" s="21"/>
+      <c r="M105" s="21"/>
+      <c r="N105" s="21"/>
       <c r="O105" s="8"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
@@ -4714,15 +4814,15 @@
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
+      <c r="F106" s="14"/>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
-      <c r="J106" s="7"/>
-      <c r="K106" s="7"/>
-      <c r="L106" s="7"/>
-      <c r="M106" s="7"/>
-      <c r="N106" s="7"/>
+      <c r="J106" s="21"/>
+      <c r="K106" s="21"/>
+      <c r="L106" s="21"/>
+      <c r="M106" s="21"/>
+      <c r="N106" s="21"/>
       <c r="O106" s="7"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
@@ -4731,15 +4831,15 @@
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
+      <c r="F107" s="15"/>
       <c r="G107" s="8"/>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
-      <c r="J107" s="8"/>
-      <c r="K107" s="8"/>
-      <c r="L107" s="8"/>
-      <c r="M107" s="8"/>
-      <c r="N107" s="8"/>
+      <c r="J107" s="21"/>
+      <c r="K107" s="21"/>
+      <c r="L107" s="21"/>
+      <c r="M107" s="21"/>
+      <c r="N107" s="21"/>
       <c r="O107" s="8"/>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
@@ -4748,15 +4848,15 @@
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
+      <c r="F108" s="14"/>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
-      <c r="J108" s="7"/>
-      <c r="K108" s="7"/>
-      <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
-      <c r="N108" s="7"/>
+      <c r="J108" s="21"/>
+      <c r="K108" s="21"/>
+      <c r="L108" s="21"/>
+      <c r="M108" s="21"/>
+      <c r="N108" s="21"/>
       <c r="O108" s="7"/>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
@@ -4765,15 +4865,15 @@
       <c r="C109" s="8"/>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
+      <c r="F109" s="15"/>
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
-      <c r="J109" s="8"/>
-      <c r="K109" s="8"/>
-      <c r="L109" s="8"/>
-      <c r="M109" s="8"/>
-      <c r="N109" s="8"/>
+      <c r="J109" s="21"/>
+      <c r="K109" s="21"/>
+      <c r="L109" s="21"/>
+      <c r="M109" s="21"/>
+      <c r="N109" s="21"/>
       <c r="O109" s="8"/>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
@@ -4782,15 +4882,15 @@
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
+      <c r="F110" s="14"/>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
-      <c r="J110" s="7"/>
-      <c r="K110" s="7"/>
-      <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
-      <c r="N110" s="7"/>
+      <c r="J110" s="21"/>
+      <c r="K110" s="21"/>
+      <c r="L110" s="21"/>
+      <c r="M110" s="21"/>
+      <c r="N110" s="21"/>
       <c r="O110" s="7"/>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
@@ -4799,15 +4899,15 @@
       <c r="C111" s="8"/>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
+      <c r="F111" s="15"/>
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
-      <c r="J111" s="8"/>
-      <c r="K111" s="8"/>
-      <c r="L111" s="8"/>
-      <c r="M111" s="8"/>
-      <c r="N111" s="8"/>
+      <c r="J111" s="21"/>
+      <c r="K111" s="21"/>
+      <c r="L111" s="21"/>
+      <c r="M111" s="21"/>
+      <c r="N111" s="21"/>
       <c r="O111" s="8"/>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
@@ -4816,15 +4916,15 @@
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
+      <c r="F112" s="14"/>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
-      <c r="J112" s="7"/>
-      <c r="K112" s="7"/>
-      <c r="L112" s="7"/>
-      <c r="M112" s="7"/>
-      <c r="N112" s="7"/>
+      <c r="J112" s="21"/>
+      <c r="K112" s="21"/>
+      <c r="L112" s="21"/>
+      <c r="M112" s="21"/>
+      <c r="N112" s="21"/>
       <c r="O112" s="7"/>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
@@ -4833,15 +4933,15 @@
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
+      <c r="F113" s="15"/>
       <c r="G113" s="8"/>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
-      <c r="J113" s="8"/>
-      <c r="K113" s="8"/>
-      <c r="L113" s="8"/>
-      <c r="M113" s="8"/>
-      <c r="N113" s="8"/>
+      <c r="J113" s="21"/>
+      <c r="K113" s="21"/>
+      <c r="L113" s="21"/>
+      <c r="M113" s="21"/>
+      <c r="N113" s="21"/>
       <c r="O113" s="8"/>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
@@ -4850,15 +4950,15 @@
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
+      <c r="F114" s="14"/>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
-      <c r="J114" s="7"/>
-      <c r="K114" s="7"/>
-      <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
-      <c r="N114" s="7"/>
+      <c r="J114" s="21"/>
+      <c r="K114" s="21"/>
+      <c r="L114" s="21"/>
+      <c r="M114" s="21"/>
+      <c r="N114" s="21"/>
       <c r="O114" s="7"/>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
@@ -4867,15 +4967,15 @@
       <c r="C115" s="8"/>
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
+      <c r="F115" s="15"/>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
       <c r="I115" s="8"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="8"/>
-      <c r="L115" s="8"/>
-      <c r="M115" s="8"/>
-      <c r="N115" s="8"/>
+      <c r="J115" s="21"/>
+      <c r="K115" s="21"/>
+      <c r="L115" s="21"/>
+      <c r="M115" s="21"/>
+      <c r="N115" s="21"/>
       <c r="O115" s="8"/>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
@@ -4884,15 +4984,15 @@
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
+      <c r="F116" s="14"/>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="7"/>
-      <c r="J116" s="7"/>
-      <c r="K116" s="7"/>
-      <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
-      <c r="N116" s="7"/>
+      <c r="J116" s="21"/>
+      <c r="K116" s="21"/>
+      <c r="L116" s="21"/>
+      <c r="M116" s="21"/>
+      <c r="N116" s="21"/>
       <c r="O116" s="7"/>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
@@ -4901,15 +5001,15 @@
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
+      <c r="F117" s="15"/>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
       <c r="I117" s="8"/>
-      <c r="J117" s="8"/>
-      <c r="K117" s="8"/>
-      <c r="L117" s="8"/>
-      <c r="M117" s="8"/>
-      <c r="N117" s="8"/>
+      <c r="J117" s="21"/>
+      <c r="K117" s="21"/>
+      <c r="L117" s="21"/>
+      <c r="M117" s="21"/>
+      <c r="N117" s="21"/>
       <c r="O117" s="8"/>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
@@ -4918,15 +5018,15 @@
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
+      <c r="F118" s="14"/>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="7"/>
-      <c r="J118" s="7"/>
-      <c r="K118" s="7"/>
-      <c r="L118" s="7"/>
-      <c r="M118" s="7"/>
-      <c r="N118" s="7"/>
+      <c r="J118" s="21"/>
+      <c r="K118" s="21"/>
+      <c r="L118" s="21"/>
+      <c r="M118" s="21"/>
+      <c r="N118" s="21"/>
       <c r="O118" s="7"/>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
@@ -4935,15 +5035,15 @@
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
+      <c r="F119" s="15"/>
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
       <c r="I119" s="8"/>
-      <c r="J119" s="8"/>
-      <c r="K119" s="8"/>
-      <c r="L119" s="8"/>
-      <c r="M119" s="8"/>
-      <c r="N119" s="8"/>
+      <c r="J119" s="21"/>
+      <c r="K119" s="21"/>
+      <c r="L119" s="21"/>
+      <c r="M119" s="21"/>
+      <c r="N119" s="21"/>
       <c r="O119" s="8"/>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
@@ -4952,15 +5052,15 @@
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
+      <c r="F120" s="14"/>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
       <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
+      <c r="J120" s="21"/>
+      <c r="K120" s="21"/>
+      <c r="L120" s="21"/>
+      <c r="M120" s="21"/>
+      <c r="N120" s="21"/>
       <c r="O120" s="7"/>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
@@ -4969,15 +5069,15 @@
       <c r="C121" s="8"/>
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
+      <c r="F121" s="15"/>
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
       <c r="I121" s="8"/>
-      <c r="J121" s="8"/>
-      <c r="K121" s="8"/>
-      <c r="L121" s="8"/>
-      <c r="M121" s="8"/>
-      <c r="N121" s="8"/>
+      <c r="J121" s="21"/>
+      <c r="K121" s="21"/>
+      <c r="L121" s="21"/>
+      <c r="M121" s="21"/>
+      <c r="N121" s="21"/>
       <c r="O121" s="8"/>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
@@ -4986,15 +5086,15 @@
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
+      <c r="F122" s="14"/>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
       <c r="I122" s="7"/>
-      <c r="J122" s="7"/>
-      <c r="K122" s="7"/>
-      <c r="L122" s="7"/>
-      <c r="M122" s="7"/>
-      <c r="N122" s="7"/>
+      <c r="J122" s="21"/>
+      <c r="K122" s="21"/>
+      <c r="L122" s="21"/>
+      <c r="M122" s="21"/>
+      <c r="N122" s="21"/>
       <c r="O122" s="7"/>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
@@ -5003,15 +5103,15 @@
       <c r="C123" s="8"/>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
+      <c r="F123" s="15"/>
       <c r="G123" s="8"/>
       <c r="H123" s="8"/>
       <c r="I123" s="8"/>
-      <c r="J123" s="8"/>
-      <c r="K123" s="8"/>
-      <c r="L123" s="8"/>
-      <c r="M123" s="8"/>
-      <c r="N123" s="8"/>
+      <c r="J123" s="21"/>
+      <c r="K123" s="21"/>
+      <c r="L123" s="21"/>
+      <c r="M123" s="21"/>
+      <c r="N123" s="21"/>
       <c r="O123" s="8"/>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
@@ -5020,15 +5120,15 @@
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
+      <c r="F124" s="14"/>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
       <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
+      <c r="J124" s="21"/>
+      <c r="K124" s="21"/>
+      <c r="L124" s="21"/>
+      <c r="M124" s="21"/>
+      <c r="N124" s="21"/>
       <c r="O124" s="7"/>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
@@ -5037,15 +5137,15 @@
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
+      <c r="F125" s="15"/>
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
       <c r="I125" s="8"/>
-      <c r="J125" s="8"/>
-      <c r="K125" s="8"/>
-      <c r="L125" s="8"/>
-      <c r="M125" s="8"/>
-      <c r="N125" s="8"/>
+      <c r="J125" s="21"/>
+      <c r="K125" s="21"/>
+      <c r="L125" s="21"/>
+      <c r="M125" s="21"/>
+      <c r="N125" s="21"/>
       <c r="O125" s="8"/>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
@@ -5054,15 +5154,15 @@
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
+      <c r="F126" s="14"/>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
       <c r="I126" s="7"/>
-      <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
-      <c r="N126" s="7"/>
+      <c r="J126" s="21"/>
+      <c r="K126" s="21"/>
+      <c r="L126" s="21"/>
+      <c r="M126" s="21"/>
+      <c r="N126" s="21"/>
       <c r="O126" s="7"/>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
@@ -5071,15 +5171,15 @@
       <c r="C127" s="8"/>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
+      <c r="F127" s="15"/>
       <c r="G127" s="8"/>
       <c r="H127" s="8"/>
       <c r="I127" s="8"/>
-      <c r="J127" s="8"/>
-      <c r="K127" s="8"/>
-      <c r="L127" s="8"/>
-      <c r="M127" s="8"/>
-      <c r="N127" s="8"/>
+      <c r="J127" s="21"/>
+      <c r="K127" s="21"/>
+      <c r="L127" s="21"/>
+      <c r="M127" s="21"/>
+      <c r="N127" s="21"/>
       <c r="O127" s="8"/>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
@@ -5088,15 +5188,15 @@
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
+      <c r="F128" s="14"/>
       <c r="G128" s="7"/>
       <c r="H128" s="7"/>
       <c r="I128" s="7"/>
-      <c r="J128" s="7"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
+      <c r="J128" s="21"/>
+      <c r="K128" s="21"/>
+      <c r="L128" s="21"/>
+      <c r="M128" s="21"/>
+      <c r="N128" s="21"/>
       <c r="O128" s="7"/>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
@@ -5105,15 +5205,15 @@
       <c r="C129" s="8"/>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
+      <c r="F129" s="15"/>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
       <c r="I129" s="8"/>
-      <c r="J129" s="8"/>
-      <c r="K129" s="8"/>
-      <c r="L129" s="8"/>
-      <c r="M129" s="8"/>
-      <c r="N129" s="8"/>
+      <c r="J129" s="21"/>
+      <c r="K129" s="21"/>
+      <c r="L129" s="21"/>
+      <c r="M129" s="21"/>
+      <c r="N129" s="21"/>
       <c r="O129" s="8"/>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
@@ -5122,15 +5222,15 @@
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
+      <c r="F130" s="14"/>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
       <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
-      <c r="N130" s="7"/>
+      <c r="J130" s="21"/>
+      <c r="K130" s="21"/>
+      <c r="L130" s="21"/>
+      <c r="M130" s="21"/>
+      <c r="N130" s="21"/>
       <c r="O130" s="7"/>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
@@ -5139,15 +5239,15 @@
       <c r="C131" s="8"/>
       <c r="D131" s="8"/>
       <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
+      <c r="F131" s="15"/>
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
       <c r="I131" s="8"/>
-      <c r="J131" s="8"/>
-      <c r="K131" s="8"/>
-      <c r="L131" s="8"/>
-      <c r="M131" s="8"/>
-      <c r="N131" s="8"/>
+      <c r="J131" s="21"/>
+      <c r="K131" s="21"/>
+      <c r="L131" s="21"/>
+      <c r="M131" s="21"/>
+      <c r="N131" s="21"/>
       <c r="O131" s="8"/>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
@@ -5156,15 +5256,15 @@
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
+      <c r="F132" s="14"/>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
       <c r="I132" s="7"/>
-      <c r="J132" s="7"/>
-      <c r="K132" s="7"/>
-      <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
-      <c r="N132" s="7"/>
+      <c r="J132" s="21"/>
+      <c r="K132" s="21"/>
+      <c r="L132" s="21"/>
+      <c r="M132" s="21"/>
+      <c r="N132" s="21"/>
       <c r="O132" s="7"/>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
@@ -5173,15 +5273,15 @@
       <c r="C133" s="8"/>
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
+      <c r="F133" s="15"/>
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
       <c r="I133" s="8"/>
-      <c r="J133" s="8"/>
-      <c r="K133" s="8"/>
-      <c r="L133" s="8"/>
-      <c r="M133" s="8"/>
-      <c r="N133" s="8"/>
+      <c r="J133" s="21"/>
+      <c r="K133" s="21"/>
+      <c r="L133" s="21"/>
+      <c r="M133" s="21"/>
+      <c r="N133" s="21"/>
       <c r="O133" s="8"/>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
@@ -5190,15 +5290,15 @@
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
+      <c r="F134" s="14"/>
       <c r="G134" s="7"/>
       <c r="H134" s="7"/>
       <c r="I134" s="7"/>
-      <c r="J134" s="7"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
-      <c r="N134" s="7"/>
+      <c r="J134" s="21"/>
+      <c r="K134" s="21"/>
+      <c r="L134" s="21"/>
+      <c r="M134" s="21"/>
+      <c r="N134" s="21"/>
       <c r="O134" s="7"/>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
@@ -5207,15 +5307,15 @@
       <c r="C135" s="8"/>
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
+      <c r="F135" s="15"/>
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
       <c r="I135" s="8"/>
-      <c r="J135" s="8"/>
-      <c r="K135" s="8"/>
-      <c r="L135" s="8"/>
-      <c r="M135" s="8"/>
-      <c r="N135" s="8"/>
+      <c r="J135" s="21"/>
+      <c r="K135" s="21"/>
+      <c r="L135" s="21"/>
+      <c r="M135" s="21"/>
+      <c r="N135" s="21"/>
       <c r="O135" s="8"/>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
@@ -5224,15 +5324,15 @@
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
+      <c r="F136" s="14"/>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
       <c r="I136" s="7"/>
-      <c r="J136" s="7"/>
-      <c r="K136" s="7"/>
-      <c r="L136" s="7"/>
-      <c r="M136" s="7"/>
-      <c r="N136" s="7"/>
+      <c r="J136" s="21"/>
+      <c r="K136" s="21"/>
+      <c r="L136" s="21"/>
+      <c r="M136" s="21"/>
+      <c r="N136" s="21"/>
       <c r="O136" s="7"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
@@ -5241,15 +5341,15 @@
       <c r="C137" s="8"/>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
+      <c r="F137" s="15"/>
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
       <c r="I137" s="8"/>
-      <c r="J137" s="8"/>
-      <c r="K137" s="8"/>
-      <c r="L137" s="8"/>
-      <c r="M137" s="8"/>
-      <c r="N137" s="8"/>
+      <c r="J137" s="21"/>
+      <c r="K137" s="21"/>
+      <c r="L137" s="21"/>
+      <c r="M137" s="21"/>
+      <c r="N137" s="21"/>
       <c r="O137" s="8"/>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
@@ -5258,15 +5358,15 @@
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
+      <c r="F138" s="14"/>
       <c r="G138" s="7"/>
       <c r="H138" s="7"/>
       <c r="I138" s="7"/>
-      <c r="J138" s="7"/>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7"/>
-      <c r="M138" s="7"/>
-      <c r="N138" s="7"/>
+      <c r="J138" s="21"/>
+      <c r="K138" s="21"/>
+      <c r="L138" s="21"/>
+      <c r="M138" s="21"/>
+      <c r="N138" s="21"/>
       <c r="O138" s="7"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
@@ -5275,15 +5375,15 @@
       <c r="C139" s="8"/>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
+      <c r="F139" s="15"/>
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
       <c r="I139" s="8"/>
-      <c r="J139" s="8"/>
-      <c r="K139" s="8"/>
-      <c r="L139" s="8"/>
-      <c r="M139" s="8"/>
-      <c r="N139" s="8"/>
+      <c r="J139" s="21"/>
+      <c r="K139" s="21"/>
+      <c r="L139" s="21"/>
+      <c r="M139" s="21"/>
+      <c r="N139" s="21"/>
       <c r="O139" s="8"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
@@ -5292,15 +5392,15 @@
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
+      <c r="F140" s="14"/>
       <c r="G140" s="7"/>
       <c r="H140" s="7"/>
       <c r="I140" s="7"/>
-      <c r="J140" s="7"/>
-      <c r="K140" s="7"/>
-      <c r="L140" s="7"/>
-      <c r="M140" s="7"/>
-      <c r="N140" s="7"/>
+      <c r="J140" s="21"/>
+      <c r="K140" s="21"/>
+      <c r="L140" s="21"/>
+      <c r="M140" s="21"/>
+      <c r="N140" s="21"/>
       <c r="O140" s="7"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
@@ -5309,15 +5409,15 @@
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
+      <c r="F141" s="15"/>
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
       <c r="I141" s="8"/>
-      <c r="J141" s="8"/>
-      <c r="K141" s="8"/>
-      <c r="L141" s="8"/>
-      <c r="M141" s="8"/>
-      <c r="N141" s="8"/>
+      <c r="J141" s="21"/>
+      <c r="K141" s="21"/>
+      <c r="L141" s="21"/>
+      <c r="M141" s="21"/>
+      <c r="N141" s="21"/>
       <c r="O141" s="8"/>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
@@ -5326,15 +5426,15 @@
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
+      <c r="F142" s="14"/>
       <c r="G142" s="7"/>
       <c r="H142" s="7"/>
       <c r="I142" s="7"/>
-      <c r="J142" s="7"/>
-      <c r="K142" s="7"/>
-      <c r="L142" s="7"/>
-      <c r="M142" s="7"/>
-      <c r="N142" s="7"/>
+      <c r="J142" s="21"/>
+      <c r="K142" s="21"/>
+      <c r="L142" s="21"/>
+      <c r="M142" s="21"/>
+      <c r="N142" s="21"/>
       <c r="O142" s="7"/>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
@@ -5343,15 +5443,15 @@
       <c r="C143" s="8"/>
       <c r="D143" s="8"/>
       <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
+      <c r="F143" s="15"/>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
       <c r="I143" s="8"/>
-      <c r="J143" s="8"/>
-      <c r="K143" s="8"/>
-      <c r="L143" s="8"/>
-      <c r="M143" s="8"/>
-      <c r="N143" s="8"/>
+      <c r="J143" s="21"/>
+      <c r="K143" s="21"/>
+      <c r="L143" s="21"/>
+      <c r="M143" s="21"/>
+      <c r="N143" s="21"/>
       <c r="O143" s="8"/>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
@@ -5360,15 +5460,15 @@
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
+      <c r="F144" s="14"/>
       <c r="G144" s="7"/>
       <c r="H144" s="7"/>
       <c r="I144" s="7"/>
-      <c r="J144" s="7"/>
-      <c r="K144" s="7"/>
-      <c r="L144" s="7"/>
-      <c r="M144" s="7"/>
-      <c r="N144" s="7"/>
+      <c r="J144" s="21"/>
+      <c r="K144" s="21"/>
+      <c r="L144" s="21"/>
+      <c r="M144" s="21"/>
+      <c r="N144" s="21"/>
       <c r="O144" s="7"/>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
@@ -5377,15 +5477,15 @@
       <c r="C145" s="8"/>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
+      <c r="F145" s="15"/>
       <c r="G145" s="8"/>
       <c r="H145" s="8"/>
       <c r="I145" s="8"/>
-      <c r="J145" s="8"/>
-      <c r="K145" s="8"/>
-      <c r="L145" s="8"/>
-      <c r="M145" s="8"/>
-      <c r="N145" s="8"/>
+      <c r="J145" s="21"/>
+      <c r="K145" s="21"/>
+      <c r="L145" s="21"/>
+      <c r="M145" s="21"/>
+      <c r="N145" s="21"/>
       <c r="O145" s="8"/>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
@@ -5394,15 +5494,15 @@
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
+      <c r="F146" s="14"/>
       <c r="G146" s="7"/>
       <c r="H146" s="7"/>
       <c r="I146" s="7"/>
-      <c r="J146" s="7"/>
-      <c r="K146" s="7"/>
-      <c r="L146" s="7"/>
-      <c r="M146" s="7"/>
-      <c r="N146" s="7"/>
+      <c r="J146" s="21"/>
+      <c r="K146" s="21"/>
+      <c r="L146" s="21"/>
+      <c r="M146" s="21"/>
+      <c r="N146" s="21"/>
       <c r="O146" s="7"/>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
@@ -5411,15 +5511,15 @@
       <c r="C147" s="8"/>
       <c r="D147" s="8"/>
       <c r="E147" s="8"/>
-      <c r="F147" s="8"/>
+      <c r="F147" s="15"/>
       <c r="G147" s="8"/>
       <c r="H147" s="8"/>
       <c r="I147" s="8"/>
-      <c r="J147" s="8"/>
-      <c r="K147" s="8"/>
-      <c r="L147" s="8"/>
-      <c r="M147" s="8"/>
-      <c r="N147" s="8"/>
+      <c r="J147" s="21"/>
+      <c r="K147" s="21"/>
+      <c r="L147" s="21"/>
+      <c r="M147" s="21"/>
+      <c r="N147" s="21"/>
       <c r="O147" s="8"/>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
@@ -5428,15 +5528,15 @@
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
-      <c r="F148" s="7"/>
+      <c r="F148" s="14"/>
       <c r="G148" s="7"/>
       <c r="H148" s="7"/>
       <c r="I148" s="7"/>
-      <c r="J148" s="7"/>
-      <c r="K148" s="7"/>
-      <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
-      <c r="N148" s="7"/>
+      <c r="J148" s="21"/>
+      <c r="K148" s="21"/>
+      <c r="L148" s="21"/>
+      <c r="M148" s="21"/>
+      <c r="N148" s="21"/>
       <c r="O148" s="7"/>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
@@ -5445,15 +5545,15 @@
       <c r="C149" s="8"/>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
-      <c r="F149" s="8"/>
+      <c r="F149" s="15"/>
       <c r="G149" s="8"/>
       <c r="H149" s="8"/>
       <c r="I149" s="8"/>
-      <c r="J149" s="8"/>
-      <c r="K149" s="8"/>
-      <c r="L149" s="8"/>
-      <c r="M149" s="8"/>
-      <c r="N149" s="8"/>
+      <c r="J149" s="21"/>
+      <c r="K149" s="21"/>
+      <c r="L149" s="21"/>
+      <c r="M149" s="21"/>
+      <c r="N149" s="21"/>
       <c r="O149" s="8"/>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
@@ -5462,15 +5562,15 @@
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
+      <c r="F150" s="14"/>
       <c r="G150" s="7"/>
       <c r="H150" s="7"/>
       <c r="I150" s="7"/>
-      <c r="J150" s="7"/>
-      <c r="K150" s="7"/>
-      <c r="L150" s="7"/>
-      <c r="M150" s="7"/>
-      <c r="N150" s="7"/>
+      <c r="J150" s="21"/>
+      <c r="K150" s="21"/>
+      <c r="L150" s="21"/>
+      <c r="M150" s="21"/>
+      <c r="N150" s="21"/>
       <c r="O150" s="7"/>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
@@ -5479,15 +5579,15 @@
       <c r="C151" s="8"/>
       <c r="D151" s="8"/>
       <c r="E151" s="8"/>
-      <c r="F151" s="8"/>
+      <c r="F151" s="15"/>
       <c r="G151" s="8"/>
       <c r="H151" s="8"/>
       <c r="I151" s="8"/>
-      <c r="J151" s="8"/>
-      <c r="K151" s="8"/>
-      <c r="L151" s="8"/>
-      <c r="M151" s="8"/>
-      <c r="N151" s="8"/>
+      <c r="J151" s="21"/>
+      <c r="K151" s="21"/>
+      <c r="L151" s="21"/>
+      <c r="M151" s="21"/>
+      <c r="N151" s="21"/>
       <c r="O151" s="8"/>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
@@ -5496,15 +5596,15 @@
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
+      <c r="F152" s="14"/>
       <c r="G152" s="7"/>
       <c r="H152" s="7"/>
       <c r="I152" s="7"/>
-      <c r="J152" s="7"/>
-      <c r="K152" s="7"/>
-      <c r="L152" s="7"/>
-      <c r="M152" s="7"/>
-      <c r="N152" s="7"/>
+      <c r="J152" s="21"/>
+      <c r="K152" s="21"/>
+      <c r="L152" s="21"/>
+      <c r="M152" s="21"/>
+      <c r="N152" s="21"/>
       <c r="O152" s="7"/>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
@@ -5513,15 +5613,15 @@
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
-      <c r="F153" s="8"/>
+      <c r="F153" s="15"/>
       <c r="G153" s="8"/>
       <c r="H153" s="8"/>
       <c r="I153" s="8"/>
-      <c r="J153" s="8"/>
-      <c r="K153" s="8"/>
-      <c r="L153" s="8"/>
-      <c r="M153" s="8"/>
-      <c r="N153" s="8"/>
+      <c r="J153" s="21"/>
+      <c r="K153" s="21"/>
+      <c r="L153" s="21"/>
+      <c r="M153" s="21"/>
+      <c r="N153" s="21"/>
       <c r="O153" s="8"/>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
@@ -5530,15 +5630,15 @@
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
-      <c r="F154" s="7"/>
+      <c r="F154" s="14"/>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
       <c r="I154" s="7"/>
-      <c r="J154" s="7"/>
-      <c r="K154" s="7"/>
-      <c r="L154" s="7"/>
-      <c r="M154" s="7"/>
-      <c r="N154" s="7"/>
+      <c r="J154" s="21"/>
+      <c r="K154" s="21"/>
+      <c r="L154" s="21"/>
+      <c r="M154" s="21"/>
+      <c r="N154" s="21"/>
       <c r="O154" s="7"/>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
@@ -5547,15 +5647,15 @@
       <c r="C155" s="8"/>
       <c r="D155" s="8"/>
       <c r="E155" s="8"/>
-      <c r="F155" s="8"/>
+      <c r="F155" s="15"/>
       <c r="G155" s="8"/>
       <c r="H155" s="8"/>
       <c r="I155" s="8"/>
-      <c r="J155" s="8"/>
-      <c r="K155" s="8"/>
-      <c r="L155" s="8"/>
-      <c r="M155" s="8"/>
-      <c r="N155" s="8"/>
+      <c r="J155" s="21"/>
+      <c r="K155" s="21"/>
+      <c r="L155" s="21"/>
+      <c r="M155" s="21"/>
+      <c r="N155" s="21"/>
       <c r="O155" s="8"/>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
@@ -5564,15 +5664,15 @@
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
+      <c r="F156" s="14"/>
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
       <c r="I156" s="7"/>
-      <c r="J156" s="7"/>
-      <c r="K156" s="7"/>
-      <c r="L156" s="7"/>
-      <c r="M156" s="7"/>
-      <c r="N156" s="7"/>
+      <c r="J156" s="21"/>
+      <c r="K156" s="21"/>
+      <c r="L156" s="21"/>
+      <c r="M156" s="21"/>
+      <c r="N156" s="21"/>
       <c r="O156" s="7"/>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
@@ -5581,15 +5681,15 @@
       <c r="C157" s="8"/>
       <c r="D157" s="8"/>
       <c r="E157" s="8"/>
-      <c r="F157" s="8"/>
+      <c r="F157" s="15"/>
       <c r="G157" s="8"/>
       <c r="H157" s="8"/>
       <c r="I157" s="8"/>
-      <c r="J157" s="8"/>
-      <c r="K157" s="8"/>
-      <c r="L157" s="8"/>
-      <c r="M157" s="8"/>
-      <c r="N157" s="8"/>
+      <c r="J157" s="21"/>
+      <c r="K157" s="21"/>
+      <c r="L157" s="21"/>
+      <c r="M157" s="21"/>
+      <c r="N157" s="21"/>
       <c r="O157" s="8"/>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
@@ -5598,15 +5698,15 @@
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
+      <c r="F158" s="14"/>
       <c r="G158" s="7"/>
       <c r="H158" s="7"/>
       <c r="I158" s="7"/>
-      <c r="J158" s="7"/>
-      <c r="K158" s="7"/>
-      <c r="L158" s="7"/>
-      <c r="M158" s="7"/>
-      <c r="N158" s="7"/>
+      <c r="J158" s="21"/>
+      <c r="K158" s="21"/>
+      <c r="L158" s="21"/>
+      <c r="M158" s="21"/>
+      <c r="N158" s="21"/>
       <c r="O158" s="7"/>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
@@ -5615,15 +5715,15 @@
       <c r="C159" s="8"/>
       <c r="D159" s="8"/>
       <c r="E159" s="8"/>
-      <c r="F159" s="8"/>
+      <c r="F159" s="15"/>
       <c r="G159" s="8"/>
       <c r="H159" s="8"/>
       <c r="I159" s="8"/>
-      <c r="J159" s="8"/>
-      <c r="K159" s="8"/>
-      <c r="L159" s="8"/>
-      <c r="M159" s="8"/>
-      <c r="N159" s="8"/>
+      <c r="J159" s="21"/>
+      <c r="K159" s="21"/>
+      <c r="L159" s="21"/>
+      <c r="M159" s="21"/>
+      <c r="N159" s="21"/>
       <c r="O159" s="8"/>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
@@ -5632,15 +5732,15 @@
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
-      <c r="F160" s="7"/>
+      <c r="F160" s="14"/>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
       <c r="I160" s="7"/>
-      <c r="J160" s="7"/>
-      <c r="K160" s="7"/>
-      <c r="L160" s="7"/>
-      <c r="M160" s="7"/>
-      <c r="N160" s="7"/>
+      <c r="J160" s="21"/>
+      <c r="K160" s="21"/>
+      <c r="L160" s="21"/>
+      <c r="M160" s="21"/>
+      <c r="N160" s="21"/>
       <c r="O160" s="7"/>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
@@ -5649,15 +5749,15 @@
       <c r="C161" s="8"/>
       <c r="D161" s="8"/>
       <c r="E161" s="8"/>
-      <c r="F161" s="8"/>
+      <c r="F161" s="15"/>
       <c r="G161" s="8"/>
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
-      <c r="J161" s="8"/>
-      <c r="K161" s="8"/>
-      <c r="L161" s="8"/>
-      <c r="M161" s="8"/>
-      <c r="N161" s="8"/>
+      <c r="J161" s="21"/>
+      <c r="K161" s="21"/>
+      <c r="L161" s="21"/>
+      <c r="M161" s="21"/>
+      <c r="N161" s="21"/>
       <c r="O161" s="8"/>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
@@ -5666,15 +5766,15 @@
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
-      <c r="F162" s="7"/>
+      <c r="F162" s="14"/>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
       <c r="I162" s="7"/>
-      <c r="J162" s="7"/>
-      <c r="K162" s="7"/>
-      <c r="L162" s="7"/>
-      <c r="M162" s="7"/>
-      <c r="N162" s="7"/>
+      <c r="J162" s="21"/>
+      <c r="K162" s="21"/>
+      <c r="L162" s="21"/>
+      <c r="M162" s="21"/>
+      <c r="N162" s="21"/>
       <c r="O162" s="7"/>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
@@ -5683,15 +5783,15 @@
       <c r="C163" s="8"/>
       <c r="D163" s="8"/>
       <c r="E163" s="8"/>
-      <c r="F163" s="8"/>
+      <c r="F163" s="15"/>
       <c r="G163" s="8"/>
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
-      <c r="J163" s="8"/>
-      <c r="K163" s="8"/>
-      <c r="L163" s="8"/>
-      <c r="M163" s="8"/>
-      <c r="N163" s="8"/>
+      <c r="J163" s="21"/>
+      <c r="K163" s="21"/>
+      <c r="L163" s="21"/>
+      <c r="M163" s="21"/>
+      <c r="N163" s="21"/>
       <c r="O163" s="8"/>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
@@ -5700,15 +5800,15 @@
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
-      <c r="F164" s="7"/>
+      <c r="F164" s="14"/>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
       <c r="I164" s="7"/>
-      <c r="J164" s="7"/>
-      <c r="K164" s="7"/>
-      <c r="L164" s="7"/>
-      <c r="M164" s="7"/>
-      <c r="N164" s="7"/>
+      <c r="J164" s="21"/>
+      <c r="K164" s="21"/>
+      <c r="L164" s="21"/>
+      <c r="M164" s="21"/>
+      <c r="N164" s="21"/>
       <c r="O164" s="7"/>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
@@ -5717,15 +5817,15 @@
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
-      <c r="F165" s="8"/>
+      <c r="F165" s="15"/>
       <c r="G165" s="8"/>
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
-      <c r="J165" s="8"/>
-      <c r="K165" s="8"/>
-      <c r="L165" s="8"/>
-      <c r="M165" s="8"/>
-      <c r="N165" s="8"/>
+      <c r="J165" s="21"/>
+      <c r="K165" s="21"/>
+      <c r="L165" s="21"/>
+      <c r="M165" s="21"/>
+      <c r="N165" s="21"/>
       <c r="O165" s="8"/>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
@@ -5734,15 +5834,15 @@
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
+      <c r="F166" s="14"/>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
-      <c r="J166" s="7"/>
-      <c r="K166" s="7"/>
-      <c r="L166" s="7"/>
-      <c r="M166" s="7"/>
-      <c r="N166" s="7"/>
+      <c r="J166" s="21"/>
+      <c r="K166" s="21"/>
+      <c r="L166" s="21"/>
+      <c r="M166" s="21"/>
+      <c r="N166" s="21"/>
       <c r="O166" s="7"/>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
@@ -5751,15 +5851,15 @@
       <c r="C167" s="8"/>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
-      <c r="F167" s="8"/>
+      <c r="F167" s="15"/>
       <c r="G167" s="8"/>
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
-      <c r="J167" s="8"/>
-      <c r="K167" s="8"/>
-      <c r="L167" s="8"/>
-      <c r="M167" s="8"/>
-      <c r="N167" s="8"/>
+      <c r="J167" s="21"/>
+      <c r="K167" s="21"/>
+      <c r="L167" s="21"/>
+      <c r="M167" s="21"/>
+      <c r="N167" s="21"/>
       <c r="O167" s="8"/>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
@@ -5768,15 +5868,15 @@
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
+      <c r="F168" s="14"/>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
       <c r="I168" s="7"/>
-      <c r="J168" s="7"/>
-      <c r="K168" s="7"/>
-      <c r="L168" s="7"/>
-      <c r="M168" s="7"/>
-      <c r="N168" s="7"/>
+      <c r="J168" s="21"/>
+      <c r="K168" s="21"/>
+      <c r="L168" s="21"/>
+      <c r="M168" s="21"/>
+      <c r="N168" s="21"/>
       <c r="O168" s="7"/>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
@@ -5785,15 +5885,15 @@
       <c r="C169" s="8"/>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
-      <c r="F169" s="8"/>
+      <c r="F169" s="15"/>
       <c r="G169" s="8"/>
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
-      <c r="J169" s="8"/>
-      <c r="K169" s="8"/>
-      <c r="L169" s="8"/>
-      <c r="M169" s="8"/>
-      <c r="N169" s="8"/>
+      <c r="J169" s="21"/>
+      <c r="K169" s="21"/>
+      <c r="L169" s="21"/>
+      <c r="M169" s="21"/>
+      <c r="N169" s="21"/>
       <c r="O169" s="8"/>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
@@ -5802,15 +5902,15 @@
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
-      <c r="F170" s="7"/>
+      <c r="F170" s="14"/>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
       <c r="I170" s="7"/>
-      <c r="J170" s="7"/>
-      <c r="K170" s="7"/>
-      <c r="L170" s="7"/>
-      <c r="M170" s="7"/>
-      <c r="N170" s="7"/>
+      <c r="J170" s="21"/>
+      <c r="K170" s="21"/>
+      <c r="L170" s="21"/>
+      <c r="M170" s="21"/>
+      <c r="N170" s="21"/>
       <c r="O170" s="7"/>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
@@ -5819,15 +5919,15 @@
       <c r="C171" s="8"/>
       <c r="D171" s="8"/>
       <c r="E171" s="8"/>
-      <c r="F171" s="8"/>
+      <c r="F171" s="15"/>
       <c r="G171" s="8"/>
       <c r="H171" s="8"/>
       <c r="I171" s="8"/>
-      <c r="J171" s="8"/>
-      <c r="K171" s="8"/>
-      <c r="L171" s="8"/>
-      <c r="M171" s="8"/>
-      <c r="N171" s="8"/>
+      <c r="J171" s="21"/>
+      <c r="K171" s="21"/>
+      <c r="L171" s="21"/>
+      <c r="M171" s="21"/>
+      <c r="N171" s="21"/>
       <c r="O171" s="8"/>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
@@ -5836,15 +5936,15 @@
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
+      <c r="F172" s="14"/>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
       <c r="I172" s="7"/>
-      <c r="J172" s="7"/>
-      <c r="K172" s="7"/>
-      <c r="L172" s="7"/>
-      <c r="M172" s="7"/>
-      <c r="N172" s="7"/>
+      <c r="J172" s="21"/>
+      <c r="K172" s="21"/>
+      <c r="L172" s="21"/>
+      <c r="M172" s="21"/>
+      <c r="N172" s="21"/>
       <c r="O172" s="7"/>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
@@ -5853,15 +5953,15 @@
       <c r="C173" s="8"/>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
-      <c r="F173" s="8"/>
+      <c r="F173" s="15"/>
       <c r="G173" s="8"/>
       <c r="H173" s="8"/>
       <c r="I173" s="8"/>
-      <c r="J173" s="8"/>
-      <c r="K173" s="8"/>
-      <c r="L173" s="8"/>
-      <c r="M173" s="8"/>
-      <c r="N173" s="8"/>
+      <c r="J173" s="21"/>
+      <c r="K173" s="21"/>
+      <c r="L173" s="21"/>
+      <c r="M173" s="21"/>
+      <c r="N173" s="21"/>
       <c r="O173" s="8"/>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
@@ -5870,15 +5970,15 @@
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
+      <c r="F174" s="14"/>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
       <c r="I174" s="7"/>
-      <c r="J174" s="7"/>
-      <c r="K174" s="7"/>
-      <c r="L174" s="7"/>
-      <c r="M174" s="7"/>
-      <c r="N174" s="7"/>
+      <c r="J174" s="21"/>
+      <c r="K174" s="21"/>
+      <c r="L174" s="21"/>
+      <c r="M174" s="21"/>
+      <c r="N174" s="21"/>
       <c r="O174" s="7"/>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
@@ -5887,15 +5987,15 @@
       <c r="C175" s="8"/>
       <c r="D175" s="8"/>
       <c r="E175" s="8"/>
-      <c r="F175" s="8"/>
+      <c r="F175" s="15"/>
       <c r="G175" s="8"/>
       <c r="H175" s="8"/>
       <c r="I175" s="8"/>
-      <c r="J175" s="8"/>
-      <c r="K175" s="8"/>
-      <c r="L175" s="8"/>
-      <c r="M175" s="8"/>
-      <c r="N175" s="8"/>
+      <c r="J175" s="21"/>
+      <c r="K175" s="21"/>
+      <c r="L175" s="21"/>
+      <c r="M175" s="21"/>
+      <c r="N175" s="21"/>
       <c r="O175" s="8"/>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
@@ -5904,15 +6004,15 @@
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
-      <c r="F176" s="7"/>
+      <c r="F176" s="14"/>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
       <c r="I176" s="7"/>
-      <c r="J176" s="7"/>
-      <c r="K176" s="7"/>
-      <c r="L176" s="7"/>
-      <c r="M176" s="7"/>
-      <c r="N176" s="7"/>
+      <c r="J176" s="21"/>
+      <c r="K176" s="21"/>
+      <c r="L176" s="21"/>
+      <c r="M176" s="21"/>
+      <c r="N176" s="21"/>
       <c r="O176" s="7"/>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
@@ -5921,15 +6021,15 @@
       <c r="C177" s="8"/>
       <c r="D177" s="8"/>
       <c r="E177" s="8"/>
-      <c r="F177" s="8"/>
+      <c r="F177" s="15"/>
       <c r="G177" s="8"/>
       <c r="H177" s="8"/>
       <c r="I177" s="8"/>
-      <c r="J177" s="8"/>
-      <c r="K177" s="8"/>
-      <c r="L177" s="8"/>
-      <c r="M177" s="8"/>
-      <c r="N177" s="8"/>
+      <c r="J177" s="21"/>
+      <c r="K177" s="21"/>
+      <c r="L177" s="21"/>
+      <c r="M177" s="21"/>
+      <c r="N177" s="21"/>
       <c r="O177" s="8"/>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
@@ -5938,15 +6038,15 @@
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
-      <c r="F178" s="7"/>
+      <c r="F178" s="14"/>
       <c r="G178" s="7"/>
       <c r="H178" s="7"/>
       <c r="I178" s="7"/>
-      <c r="J178" s="7"/>
-      <c r="K178" s="7"/>
-      <c r="L178" s="7"/>
-      <c r="M178" s="7"/>
-      <c r="N178" s="7"/>
+      <c r="J178" s="21"/>
+      <c r="K178" s="21"/>
+      <c r="L178" s="21"/>
+      <c r="M178" s="21"/>
+      <c r="N178" s="21"/>
       <c r="O178" s="7"/>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
@@ -5955,15 +6055,15 @@
       <c r="C179" s="8"/>
       <c r="D179" s="8"/>
       <c r="E179" s="8"/>
-      <c r="F179" s="8"/>
+      <c r="F179" s="15"/>
       <c r="G179" s="8"/>
       <c r="H179" s="8"/>
       <c r="I179" s="8"/>
-      <c r="J179" s="8"/>
-      <c r="K179" s="8"/>
-      <c r="L179" s="8"/>
-      <c r="M179" s="8"/>
-      <c r="N179" s="8"/>
+      <c r="J179" s="21"/>
+      <c r="K179" s="21"/>
+      <c r="L179" s="21"/>
+      <c r="M179" s="21"/>
+      <c r="N179" s="21"/>
       <c r="O179" s="8"/>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
@@ -5972,15 +6072,15 @@
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
-      <c r="F180" s="7"/>
+      <c r="F180" s="14"/>
       <c r="G180" s="7"/>
       <c r="H180" s="7"/>
       <c r="I180" s="7"/>
-      <c r="J180" s="7"/>
-      <c r="K180" s="7"/>
-      <c r="L180" s="7"/>
-      <c r="M180" s="7"/>
-      <c r="N180" s="7"/>
+      <c r="J180" s="21"/>
+      <c r="K180" s="21"/>
+      <c r="L180" s="21"/>
+      <c r="M180" s="21"/>
+      <c r="N180" s="21"/>
       <c r="O180" s="7"/>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
@@ -5989,15 +6089,15 @@
       <c r="C181" s="8"/>
       <c r="D181" s="8"/>
       <c r="E181" s="8"/>
-      <c r="F181" s="8"/>
+      <c r="F181" s="15"/>
       <c r="G181" s="8"/>
       <c r="H181" s="8"/>
       <c r="I181" s="8"/>
-      <c r="J181" s="8"/>
-      <c r="K181" s="8"/>
-      <c r="L181" s="8"/>
-      <c r="M181" s="8"/>
-      <c r="N181" s="8"/>
+      <c r="J181" s="21"/>
+      <c r="K181" s="21"/>
+      <c r="L181" s="21"/>
+      <c r="M181" s="21"/>
+      <c r="N181" s="21"/>
       <c r="O181" s="8"/>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.25">
@@ -6006,15 +6106,15 @@
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
-      <c r="F182" s="7"/>
+      <c r="F182" s="14"/>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
       <c r="I182" s="7"/>
-      <c r="J182" s="7"/>
-      <c r="K182" s="7"/>
-      <c r="L182" s="7"/>
-      <c r="M182" s="7"/>
-      <c r="N182" s="7"/>
+      <c r="J182" s="21"/>
+      <c r="K182" s="21"/>
+      <c r="L182" s="21"/>
+      <c r="M182" s="21"/>
+      <c r="N182" s="21"/>
       <c r="O182" s="7"/>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
@@ -6023,15 +6123,15 @@
       <c r="C183" s="8"/>
       <c r="D183" s="8"/>
       <c r="E183" s="8"/>
-      <c r="F183" s="8"/>
+      <c r="F183" s="15"/>
       <c r="G183" s="8"/>
       <c r="H183" s="8"/>
       <c r="I183" s="8"/>
-      <c r="J183" s="8"/>
-      <c r="K183" s="8"/>
-      <c r="L183" s="8"/>
-      <c r="M183" s="8"/>
-      <c r="N183" s="8"/>
+      <c r="J183" s="21"/>
+      <c r="K183" s="21"/>
+      <c r="L183" s="21"/>
+      <c r="M183" s="21"/>
+      <c r="N183" s="21"/>
       <c r="O183" s="8"/>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
@@ -6040,15 +6140,15 @@
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
+      <c r="F184" s="14"/>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
       <c r="I184" s="7"/>
-      <c r="J184" s="7"/>
-      <c r="K184" s="7"/>
-      <c r="L184" s="7"/>
-      <c r="M184" s="7"/>
-      <c r="N184" s="7"/>
+      <c r="J184" s="21"/>
+      <c r="K184" s="21"/>
+      <c r="L184" s="21"/>
+      <c r="M184" s="21"/>
+      <c r="N184" s="21"/>
       <c r="O184" s="7"/>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
@@ -6057,15 +6157,15 @@
       <c r="C185" s="8"/>
       <c r="D185" s="8"/>
       <c r="E185" s="8"/>
-      <c r="F185" s="8"/>
+      <c r="F185" s="15"/>
       <c r="G185" s="8"/>
       <c r="H185" s="8"/>
       <c r="I185" s="8"/>
-      <c r="J185" s="8"/>
-      <c r="K185" s="8"/>
-      <c r="L185" s="8"/>
-      <c r="M185" s="8"/>
-      <c r="N185" s="8"/>
+      <c r="J185" s="21"/>
+      <c r="K185" s="21"/>
+      <c r="L185" s="21"/>
+      <c r="M185" s="21"/>
+      <c r="N185" s="21"/>
       <c r="O185" s="8"/>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
@@ -6074,15 +6174,15 @@
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
-      <c r="F186" s="7"/>
+      <c r="F186" s="14"/>
       <c r="G186" s="7"/>
       <c r="H186" s="7"/>
       <c r="I186" s="7"/>
-      <c r="J186" s="7"/>
-      <c r="K186" s="7"/>
-      <c r="L186" s="7"/>
-      <c r="M186" s="7"/>
-      <c r="N186" s="7"/>
+      <c r="J186" s="21"/>
+      <c r="K186" s="21"/>
+      <c r="L186" s="21"/>
+      <c r="M186" s="21"/>
+      <c r="N186" s="21"/>
       <c r="O186" s="7"/>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
@@ -6091,15 +6191,15 @@
       <c r="C187" s="8"/>
       <c r="D187" s="8"/>
       <c r="E187" s="8"/>
-      <c r="F187" s="8"/>
+      <c r="F187" s="15"/>
       <c r="G187" s="8"/>
       <c r="H187" s="8"/>
       <c r="I187" s="8"/>
-      <c r="J187" s="8"/>
-      <c r="K187" s="8"/>
-      <c r="L187" s="8"/>
-      <c r="M187" s="8"/>
-      <c r="N187" s="8"/>
+      <c r="J187" s="21"/>
+      <c r="K187" s="21"/>
+      <c r="L187" s="21"/>
+      <c r="M187" s="21"/>
+      <c r="N187" s="21"/>
       <c r="O187" s="8"/>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
@@ -6108,15 +6208,15 @@
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
-      <c r="F188" s="7"/>
+      <c r="F188" s="14"/>
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
       <c r="I188" s="7"/>
-      <c r="J188" s="7"/>
-      <c r="K188" s="7"/>
-      <c r="L188" s="7"/>
-      <c r="M188" s="7"/>
-      <c r="N188" s="7"/>
+      <c r="J188" s="21"/>
+      <c r="K188" s="21"/>
+      <c r="L188" s="21"/>
+      <c r="M188" s="21"/>
+      <c r="N188" s="21"/>
       <c r="O188" s="7"/>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
@@ -6125,15 +6225,15 @@
       <c r="C189" s="8"/>
       <c r="D189" s="8"/>
       <c r="E189" s="8"/>
-      <c r="F189" s="8"/>
+      <c r="F189" s="15"/>
       <c r="G189" s="8"/>
       <c r="H189" s="8"/>
       <c r="I189" s="8"/>
-      <c r="J189" s="8"/>
-      <c r="K189" s="8"/>
-      <c r="L189" s="8"/>
-      <c r="M189" s="8"/>
-      <c r="N189" s="8"/>
+      <c r="J189" s="21"/>
+      <c r="K189" s="21"/>
+      <c r="L189" s="21"/>
+      <c r="M189" s="21"/>
+      <c r="N189" s="21"/>
       <c r="O189" s="8"/>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
@@ -6142,15 +6242,15 @@
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
+      <c r="F190" s="14"/>
       <c r="G190" s="7"/>
       <c r="H190" s="7"/>
       <c r="I190" s="7"/>
-      <c r="J190" s="7"/>
-      <c r="K190" s="7"/>
-      <c r="L190" s="7"/>
-      <c r="M190" s="7"/>
-      <c r="N190" s="7"/>
+      <c r="J190" s="21"/>
+      <c r="K190" s="21"/>
+      <c r="L190" s="21"/>
+      <c r="M190" s="21"/>
+      <c r="N190" s="21"/>
       <c r="O190" s="7"/>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.25">
@@ -6159,15 +6259,15 @@
       <c r="C191" s="8"/>
       <c r="D191" s="8"/>
       <c r="E191" s="8"/>
-      <c r="F191" s="8"/>
+      <c r="F191" s="15"/>
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
       <c r="I191" s="8"/>
-      <c r="J191" s="8"/>
-      <c r="K191" s="8"/>
-      <c r="L191" s="8"/>
-      <c r="M191" s="8"/>
-      <c r="N191" s="8"/>
+      <c r="J191" s="21"/>
+      <c r="K191" s="21"/>
+      <c r="L191" s="21"/>
+      <c r="M191" s="21"/>
+      <c r="N191" s="21"/>
       <c r="O191" s="8"/>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
@@ -6176,15 +6276,15 @@
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
+      <c r="F192" s="14"/>
       <c r="G192" s="7"/>
       <c r="H192" s="7"/>
       <c r="I192" s="7"/>
-      <c r="J192" s="7"/>
-      <c r="K192" s="7"/>
-      <c r="L192" s="7"/>
-      <c r="M192" s="7"/>
-      <c r="N192" s="7"/>
+      <c r="J192" s="21"/>
+      <c r="K192" s="21"/>
+      <c r="L192" s="21"/>
+      <c r="M192" s="21"/>
+      <c r="N192" s="21"/>
       <c r="O192" s="7"/>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.25">
@@ -6193,15 +6293,15 @@
       <c r="C193" s="8"/>
       <c r="D193" s="8"/>
       <c r="E193" s="8"/>
-      <c r="F193" s="8"/>
+      <c r="F193" s="15"/>
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
       <c r="I193" s="8"/>
-      <c r="J193" s="8"/>
-      <c r="K193" s="8"/>
-      <c r="L193" s="8"/>
-      <c r="M193" s="8"/>
-      <c r="N193" s="8"/>
+      <c r="J193" s="21"/>
+      <c r="K193" s="21"/>
+      <c r="L193" s="21"/>
+      <c r="M193" s="21"/>
+      <c r="N193" s="21"/>
       <c r="O193" s="8"/>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.25">
@@ -6210,15 +6310,15 @@
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
+      <c r="F194" s="14"/>
       <c r="G194" s="7"/>
       <c r="H194" s="7"/>
       <c r="I194" s="7"/>
-      <c r="J194" s="7"/>
-      <c r="K194" s="7"/>
-      <c r="L194" s="7"/>
-      <c r="M194" s="7"/>
-      <c r="N194" s="7"/>
+      <c r="J194" s="21"/>
+      <c r="K194" s="21"/>
+      <c r="L194" s="21"/>
+      <c r="M194" s="21"/>
+      <c r="N194" s="21"/>
       <c r="O194" s="7"/>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.25">
@@ -6227,15 +6327,15 @@
       <c r="C195" s="8"/>
       <c r="D195" s="8"/>
       <c r="E195" s="8"/>
-      <c r="F195" s="8"/>
+      <c r="F195" s="15"/>
       <c r="G195" s="8"/>
       <c r="H195" s="8"/>
       <c r="I195" s="8"/>
-      <c r="J195" s="8"/>
-      <c r="K195" s="8"/>
-      <c r="L195" s="8"/>
-      <c r="M195" s="8"/>
-      <c r="N195" s="8"/>
+      <c r="J195" s="21"/>
+      <c r="K195" s="21"/>
+      <c r="L195" s="21"/>
+      <c r="M195" s="21"/>
+      <c r="N195" s="21"/>
       <c r="O195" s="8"/>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.25">
@@ -6244,15 +6344,15 @@
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
+      <c r="F196" s="14"/>
       <c r="G196" s="7"/>
       <c r="H196" s="7"/>
       <c r="I196" s="7"/>
-      <c r="J196" s="7"/>
-      <c r="K196" s="7"/>
-      <c r="L196" s="7"/>
-      <c r="M196" s="7"/>
-      <c r="N196" s="7"/>
+      <c r="J196" s="21"/>
+      <c r="K196" s="21"/>
+      <c r="L196" s="21"/>
+      <c r="M196" s="21"/>
+      <c r="N196" s="21"/>
       <c r="O196" s="7"/>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.25">
@@ -6261,15 +6361,15 @@
       <c r="C197" s="8"/>
       <c r="D197" s="8"/>
       <c r="E197" s="8"/>
-      <c r="F197" s="8"/>
+      <c r="F197" s="15"/>
       <c r="G197" s="8"/>
       <c r="H197" s="8"/>
       <c r="I197" s="8"/>
-      <c r="J197" s="8"/>
-      <c r="K197" s="8"/>
-      <c r="L197" s="8"/>
-      <c r="M197" s="8"/>
-      <c r="N197" s="8"/>
+      <c r="J197" s="21"/>
+      <c r="K197" s="21"/>
+      <c r="L197" s="21"/>
+      <c r="M197" s="21"/>
+      <c r="N197" s="21"/>
       <c r="O197" s="8"/>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.25">
@@ -6278,15 +6378,15 @@
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7"/>
-      <c r="F198" s="7"/>
+      <c r="F198" s="14"/>
       <c r="G198" s="7"/>
       <c r="H198" s="7"/>
       <c r="I198" s="7"/>
-      <c r="J198" s="7"/>
-      <c r="K198" s="7"/>
-      <c r="L198" s="7"/>
-      <c r="M198" s="7"/>
-      <c r="N198" s="7"/>
+      <c r="J198" s="21"/>
+      <c r="K198" s="21"/>
+      <c r="L198" s="21"/>
+      <c r="M198" s="21"/>
+      <c r="N198" s="21"/>
       <c r="O198" s="7"/>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.25">
@@ -6295,15 +6395,15 @@
       <c r="C199" s="8"/>
       <c r="D199" s="8"/>
       <c r="E199" s="8"/>
-      <c r="F199" s="8"/>
+      <c r="F199" s="15"/>
       <c r="G199" s="8"/>
       <c r="H199" s="8"/>
       <c r="I199" s="8"/>
-      <c r="J199" s="8"/>
-      <c r="K199" s="8"/>
-      <c r="L199" s="8"/>
-      <c r="M199" s="8"/>
-      <c r="N199" s="8"/>
+      <c r="J199" s="21"/>
+      <c r="K199" s="21"/>
+      <c r="L199" s="21"/>
+      <c r="M199" s="21"/>
+      <c r="N199" s="21"/>
       <c r="O199" s="8"/>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.25">
@@ -6312,15 +6412,15 @@
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
+      <c r="F200" s="14"/>
       <c r="G200" s="7"/>
       <c r="H200" s="7"/>
       <c r="I200" s="7"/>
-      <c r="J200" s="7"/>
-      <c r="K200" s="7"/>
-      <c r="L200" s="7"/>
-      <c r="M200" s="7"/>
-      <c r="N200" s="7"/>
+      <c r="J200" s="21"/>
+      <c r="K200" s="21"/>
+      <c r="L200" s="21"/>
+      <c r="M200" s="21"/>
+      <c r="N200" s="21"/>
       <c r="O200" s="7"/>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.25">
@@ -6329,15 +6429,15 @@
       <c r="C201" s="8"/>
       <c r="D201" s="8"/>
       <c r="E201" s="8"/>
-      <c r="F201" s="8"/>
+      <c r="F201" s="15"/>
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
       <c r="I201" s="8"/>
-      <c r="J201" s="8"/>
-      <c r="K201" s="8"/>
-      <c r="L201" s="8"/>
-      <c r="M201" s="8"/>
-      <c r="N201" s="8"/>
+      <c r="J201" s="21"/>
+      <c r="K201" s="21"/>
+      <c r="L201" s="21"/>
+      <c r="M201" s="21"/>
+      <c r="N201" s="21"/>
       <c r="O201" s="8"/>
     </row>
   </sheetData>
@@ -6370,34 +6470,34 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="C2" s="11"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8210,36 +8310,37 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="4" width="12" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12" style="22" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>51</v>
+      <c r="D1" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
     </row>
@@ -8247,7 +8348,7 @@
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
     </row>
@@ -8255,7 +8356,7 @@
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
@@ -8263,7 +8364,7 @@
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
     </row>
@@ -8271,7 +8372,7 @@
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
@@ -8279,7 +8380,7 @@
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
     </row>
@@ -8287,7 +8388,7 @@
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
     </row>
@@ -8295,7 +8396,7 @@
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
@@ -8303,7 +8404,7 @@
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
     </row>
@@ -8311,7 +8412,7 @@
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
@@ -8319,7 +8420,7 @@
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
     </row>
@@ -8327,7 +8428,7 @@
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
@@ -8335,7 +8436,7 @@
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
@@ -8343,7 +8444,7 @@
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
@@ -8351,7 +8452,7 @@
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
@@ -8359,7 +8460,7 @@
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
@@ -8367,7 +8468,7 @@
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
@@ -8375,7 +8476,7 @@
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
@@ -8383,7 +8484,7 @@
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
@@ -8391,7 +8492,7 @@
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
@@ -8399,7 +8500,7 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
@@ -8407,7 +8508,7 @@
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
     </row>
@@ -8415,7 +8516,7 @@
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
@@ -8423,7 +8524,7 @@
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
@@ -8431,7 +8532,7 @@
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
@@ -8439,7 +8540,7 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
@@ -8447,7 +8548,7 @@
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
     </row>
@@ -8455,7 +8556,7 @@
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
     </row>
@@ -8463,7 +8564,7 @@
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
     </row>
@@ -8471,7 +8572,7 @@
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
@@ -8479,7 +8580,7 @@
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
@@ -8487,7 +8588,7 @@
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
@@ -8495,7 +8596,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
     </row>
@@ -8503,7 +8604,7 @@
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
     </row>
@@ -8511,7 +8612,7 @@
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
     </row>
@@ -8519,7 +8620,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
@@ -8527,7 +8628,7 @@
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
     </row>
@@ -8535,7 +8636,7 @@
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
@@ -8543,7 +8644,7 @@
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
     </row>
@@ -8551,7 +8652,7 @@
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
     </row>
@@ -8559,7 +8660,7 @@
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
     </row>
@@ -8567,7 +8668,7 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
@@ -8575,7 +8676,7 @@
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
     </row>
@@ -8583,7 +8684,7 @@
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
     </row>
@@ -8591,7 +8692,7 @@
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
     </row>
@@ -8599,7 +8700,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
@@ -8607,7 +8708,7 @@
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
     </row>
@@ -8615,7 +8716,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
@@ -8623,7 +8724,7 @@
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
     </row>
@@ -8631,7 +8732,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
@@ -8639,7 +8740,7 @@
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
     </row>
@@ -8647,7 +8748,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
@@ -8655,7 +8756,7 @@
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
     </row>
@@ -8663,7 +8764,7 @@
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
@@ -8671,7 +8772,7 @@
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
     </row>
@@ -8679,7 +8780,7 @@
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
@@ -8687,7 +8788,7 @@
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
+      <c r="D58" s="21"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
     </row>
@@ -8695,7 +8796,7 @@
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
+      <c r="D59" s="21"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
@@ -8703,7 +8804,7 @@
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
+      <c r="D60" s="21"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
     </row>
@@ -8711,7 +8812,7 @@
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
+      <c r="D61" s="21"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
     </row>
@@ -8719,7 +8820,7 @@
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
+      <c r="D62" s="21"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
     </row>
@@ -8727,7 +8828,7 @@
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
+      <c r="D63" s="21"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
@@ -8735,7 +8836,7 @@
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
+      <c r="D64" s="21"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
     </row>
@@ -8743,7 +8844,7 @@
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
+      <c r="D65" s="21"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
     </row>
@@ -8751,7 +8852,7 @@
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
+      <c r="D66" s="21"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
     </row>
@@ -8759,7 +8860,7 @@
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
+      <c r="D67" s="21"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
     </row>
@@ -8767,7 +8868,7 @@
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
+      <c r="D68" s="21"/>
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
     </row>
@@ -8775,7 +8876,7 @@
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
+      <c r="D69" s="21"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
     </row>
@@ -8783,7 +8884,7 @@
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
+      <c r="D70" s="21"/>
       <c r="E70" s="7"/>
       <c r="F70" s="7"/>
     </row>
@@ -8791,7 +8892,7 @@
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
+      <c r="D71" s="21"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
     </row>
@@ -8799,7 +8900,7 @@
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
+      <c r="D72" s="21"/>
       <c r="E72" s="7"/>
       <c r="F72" s="7"/>
     </row>
@@ -8807,7 +8908,7 @@
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
+      <c r="D73" s="21"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
     </row>
@@ -8815,7 +8916,7 @@
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
+      <c r="D74" s="21"/>
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
     </row>
@@ -8823,7 +8924,7 @@
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
+      <c r="D75" s="21"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
     </row>
@@ -8831,7 +8932,7 @@
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
+      <c r="D76" s="21"/>
       <c r="E76" s="7"/>
       <c r="F76" s="7"/>
     </row>
@@ -8839,7 +8940,7 @@
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
+      <c r="D77" s="21"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
@@ -8847,7 +8948,7 @@
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
+      <c r="D78" s="21"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
     </row>
@@ -8855,7 +8956,7 @@
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
+      <c r="D79" s="21"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
     </row>
@@ -8863,7 +8964,7 @@
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
+      <c r="D80" s="21"/>
       <c r="E80" s="7"/>
       <c r="F80" s="7"/>
     </row>
@@ -8871,7 +8972,7 @@
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
+      <c r="D81" s="21"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
     </row>
@@ -8879,7 +8980,7 @@
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
+      <c r="D82" s="21"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
     </row>
@@ -8887,7 +8988,7 @@
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
+      <c r="D83" s="21"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
     </row>
@@ -8895,7 +8996,7 @@
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
+      <c r="D84" s="21"/>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
     </row>
@@ -8903,7 +9004,7 @@
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
+      <c r="D85" s="21"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
     </row>
@@ -8911,7 +9012,7 @@
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
+      <c r="D86" s="21"/>
       <c r="E86" s="7"/>
       <c r="F86" s="7"/>
     </row>
@@ -8919,7 +9020,7 @@
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
+      <c r="D87" s="21"/>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
     </row>
@@ -8927,7 +9028,7 @@
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
+      <c r="D88" s="21"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7"/>
     </row>
@@ -8935,7 +9036,7 @@
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
+      <c r="D89" s="21"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
     </row>
@@ -8943,7 +9044,7 @@
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
+      <c r="D90" s="21"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7"/>
     </row>
@@ -8951,7 +9052,7 @@
       <c r="A91" s="8"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
+      <c r="D91" s="21"/>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
     </row>
@@ -8959,7 +9060,7 @@
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
+      <c r="D92" s="21"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7"/>
     </row>
@@ -8967,7 +9068,7 @@
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
+      <c r="D93" s="21"/>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
     </row>
@@ -8975,7 +9076,7 @@
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
+      <c r="D94" s="21"/>
       <c r="E94" s="7"/>
       <c r="F94" s="7"/>
     </row>
@@ -8983,7 +9084,7 @@
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
+      <c r="D95" s="21"/>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
     </row>
@@ -8991,7 +9092,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
+      <c r="D96" s="21"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7"/>
     </row>
@@ -8999,7 +9100,7 @@
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
+      <c r="D97" s="21"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
     </row>
@@ -9007,7 +9108,7 @@
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
+      <c r="D98" s="21"/>
       <c r="E98" s="7"/>
       <c r="F98" s="7"/>
     </row>
@@ -9015,7 +9116,7 @@
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
+      <c r="D99" s="21"/>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
     </row>
@@ -9023,7 +9124,7 @@
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
+      <c r="D100" s="21"/>
       <c r="E100" s="7"/>
       <c r="F100" s="7"/>
     </row>
@@ -9031,7 +9132,7 @@
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
+      <c r="D101" s="21"/>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
     </row>
@@ -9039,7 +9140,7 @@
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
+      <c r="D102" s="21"/>
       <c r="E102" s="7"/>
       <c r="F102" s="7"/>
     </row>
@@ -9047,7 +9148,7 @@
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
+      <c r="D103" s="21"/>
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
     </row>
@@ -9055,7 +9156,7 @@
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
+      <c r="D104" s="21"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7"/>
     </row>
@@ -9063,7 +9164,7 @@
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
+      <c r="D105" s="21"/>
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
     </row>
@@ -9071,7 +9172,7 @@
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
+      <c r="D106" s="21"/>
       <c r="E106" s="7"/>
       <c r="F106" s="7"/>
     </row>
@@ -9079,7 +9180,7 @@
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
+      <c r="D107" s="21"/>
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
     </row>
@@ -9087,7 +9188,7 @@
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
+      <c r="D108" s="21"/>
       <c r="E108" s="7"/>
       <c r="F108" s="7"/>
     </row>
@@ -9095,7 +9196,7 @@
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
+      <c r="D109" s="21"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
     </row>
@@ -9103,7 +9204,7 @@
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
+      <c r="D110" s="21"/>
       <c r="E110" s="7"/>
       <c r="F110" s="7"/>
     </row>
@@ -9111,7 +9212,7 @@
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
+      <c r="D111" s="21"/>
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
     </row>
@@ -9119,7 +9220,7 @@
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
+      <c r="D112" s="21"/>
       <c r="E112" s="7"/>
       <c r="F112" s="7"/>
     </row>
@@ -9127,7 +9228,7 @@
       <c r="A113" s="8"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
+      <c r="D113" s="21"/>
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
     </row>
@@ -9135,7 +9236,7 @@
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
+      <c r="D114" s="21"/>
       <c r="E114" s="7"/>
       <c r="F114" s="7"/>
     </row>
@@ -9143,7 +9244,7 @@
       <c r="A115" s="8"/>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
+      <c r="D115" s="21"/>
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
     </row>
@@ -9151,7 +9252,7 @@
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
+      <c r="D116" s="21"/>
       <c r="E116" s="7"/>
       <c r="F116" s="7"/>
     </row>
@@ -9159,7 +9260,7 @@
       <c r="A117" s="8"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
+      <c r="D117" s="21"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
     </row>
@@ -9167,7 +9268,7 @@
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
+      <c r="D118" s="21"/>
       <c r="E118" s="7"/>
       <c r="F118" s="7"/>
     </row>
@@ -9175,7 +9276,7 @@
       <c r="A119" s="8"/>
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
+      <c r="D119" s="21"/>
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
     </row>
@@ -9183,7 +9284,7 @@
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
+      <c r="D120" s="21"/>
       <c r="E120" s="7"/>
       <c r="F120" s="7"/>
     </row>
@@ -9191,7 +9292,7 @@
       <c r="A121" s="8"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
+      <c r="D121" s="21"/>
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
     </row>
@@ -9199,7 +9300,7 @@
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
+      <c r="D122" s="21"/>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
     </row>
@@ -9207,7 +9308,7 @@
       <c r="A123" s="8"/>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
+      <c r="D123" s="21"/>
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
     </row>
@@ -9215,7 +9316,7 @@
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
+      <c r="D124" s="21"/>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
     </row>
@@ -9223,7 +9324,7 @@
       <c r="A125" s="8"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
+      <c r="D125" s="21"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
     </row>
@@ -9231,7 +9332,7 @@
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
+      <c r="D126" s="21"/>
       <c r="E126" s="7"/>
       <c r="F126" s="7"/>
     </row>
@@ -9239,7 +9340,7 @@
       <c r="A127" s="8"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
+      <c r="D127" s="21"/>
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
     </row>
@@ -9247,7 +9348,7 @@
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
+      <c r="D128" s="21"/>
       <c r="E128" s="7"/>
       <c r="F128" s="7"/>
     </row>
@@ -9255,7 +9356,7 @@
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
+      <c r="D129" s="21"/>
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
     </row>
@@ -9263,7 +9364,7 @@
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
+      <c r="D130" s="21"/>
       <c r="E130" s="7"/>
       <c r="F130" s="7"/>
     </row>
@@ -9271,7 +9372,7 @@
       <c r="A131" s="8"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
+      <c r="D131" s="21"/>
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
     </row>
@@ -9279,7 +9380,7 @@
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
+      <c r="D132" s="21"/>
       <c r="E132" s="7"/>
       <c r="F132" s="7"/>
     </row>
@@ -9287,7 +9388,7 @@
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
+      <c r="D133" s="21"/>
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
     </row>
@@ -9295,7 +9396,7 @@
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
+      <c r="D134" s="21"/>
       <c r="E134" s="7"/>
       <c r="F134" s="7"/>
     </row>
@@ -9303,7 +9404,7 @@
       <c r="A135" s="8"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
+      <c r="D135" s="21"/>
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
     </row>
@@ -9311,7 +9412,7 @@
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
+      <c r="D136" s="21"/>
       <c r="E136" s="7"/>
       <c r="F136" s="7"/>
     </row>
@@ -9319,7 +9420,7 @@
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
+      <c r="D137" s="21"/>
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
     </row>
@@ -9327,7 +9428,7 @@
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
+      <c r="D138" s="21"/>
       <c r="E138" s="7"/>
       <c r="F138" s="7"/>
     </row>
@@ -9335,7 +9436,7 @@
       <c r="A139" s="8"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
+      <c r="D139" s="21"/>
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
     </row>
@@ -9343,7 +9444,7 @@
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
+      <c r="D140" s="21"/>
       <c r="E140" s="7"/>
       <c r="F140" s="7"/>
     </row>
@@ -9351,7 +9452,7 @@
       <c r="A141" s="8"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
+      <c r="D141" s="21"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
     </row>
@@ -9359,7 +9460,7 @@
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
+      <c r="D142" s="21"/>
       <c r="E142" s="7"/>
       <c r="F142" s="7"/>
     </row>
@@ -9367,7 +9468,7 @@
       <c r="A143" s="8"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
+      <c r="D143" s="21"/>
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
     </row>
@@ -9375,7 +9476,7 @@
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
+      <c r="D144" s="21"/>
       <c r="E144" s="7"/>
       <c r="F144" s="7"/>
     </row>
@@ -9383,7 +9484,7 @@
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
+      <c r="D145" s="21"/>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
     </row>
@@ -9391,7 +9492,7 @@
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
+      <c r="D146" s="21"/>
       <c r="E146" s="7"/>
       <c r="F146" s="7"/>
     </row>
@@ -9399,7 +9500,7 @@
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
+      <c r="D147" s="21"/>
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
     </row>
@@ -9407,7 +9508,7 @@
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
+      <c r="D148" s="21"/>
       <c r="E148" s="7"/>
       <c r="F148" s="7"/>
     </row>
@@ -9415,7 +9516,7 @@
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
+      <c r="D149" s="21"/>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
     </row>
@@ -9423,7 +9524,7 @@
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
+      <c r="D150" s="21"/>
       <c r="E150" s="7"/>
       <c r="F150" s="7"/>
     </row>
@@ -9431,7 +9532,7 @@
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
+      <c r="D151" s="21"/>
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
     </row>
@@ -9439,7 +9540,7 @@
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
+      <c r="D152" s="21"/>
       <c r="E152" s="7"/>
       <c r="F152" s="7"/>
     </row>
@@ -9447,7 +9548,7 @@
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
+      <c r="D153" s="21"/>
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
     </row>
@@ -9455,7 +9556,7 @@
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
+      <c r="D154" s="21"/>
       <c r="E154" s="7"/>
       <c r="F154" s="7"/>
     </row>
@@ -9463,7 +9564,7 @@
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
+      <c r="D155" s="21"/>
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
     </row>
@@ -9471,7 +9572,7 @@
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
+      <c r="D156" s="21"/>
       <c r="E156" s="7"/>
       <c r="F156" s="7"/>
     </row>
@@ -9479,7 +9580,7 @@
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
+      <c r="D157" s="21"/>
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
     </row>
@@ -9487,7 +9588,7 @@
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
+      <c r="D158" s="21"/>
       <c r="E158" s="7"/>
       <c r="F158" s="7"/>
     </row>
@@ -9495,7 +9596,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
+      <c r="D159" s="21"/>
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
     </row>
@@ -9503,7 +9604,7 @@
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
+      <c r="D160" s="21"/>
       <c r="E160" s="7"/>
       <c r="F160" s="7"/>
     </row>
@@ -9511,7 +9612,7 @@
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
+      <c r="D161" s="21"/>
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
     </row>
@@ -9519,7 +9620,7 @@
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
+      <c r="D162" s="21"/>
       <c r="E162" s="7"/>
       <c r="F162" s="7"/>
     </row>
@@ -9527,7 +9628,7 @@
       <c r="A163" s="8"/>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
+      <c r="D163" s="21"/>
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
     </row>
@@ -9535,7 +9636,7 @@
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
-      <c r="D164" s="7"/>
+      <c r="D164" s="21"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7"/>
     </row>
@@ -9543,7 +9644,7 @@
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
+      <c r="D165" s="21"/>
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
     </row>
@@ -9551,7 +9652,7 @@
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
+      <c r="D166" s="21"/>
       <c r="E166" s="7"/>
       <c r="F166" s="7"/>
     </row>
@@ -9559,7 +9660,7 @@
       <c r="A167" s="8"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
+      <c r="D167" s="21"/>
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
     </row>
@@ -9567,7 +9668,7 @@
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
+      <c r="D168" s="21"/>
       <c r="E168" s="7"/>
       <c r="F168" s="7"/>
     </row>
@@ -9575,7 +9676,7 @@
       <c r="A169" s="8"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
+      <c r="D169" s="21"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
     </row>
@@ -9583,7 +9684,7 @@
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
+      <c r="D170" s="21"/>
       <c r="E170" s="7"/>
       <c r="F170" s="7"/>
     </row>
@@ -9591,7 +9692,7 @@
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
+      <c r="D171" s="21"/>
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
     </row>
@@ -9599,7 +9700,7 @@
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
-      <c r="D172" s="7"/>
+      <c r="D172" s="21"/>
       <c r="E172" s="7"/>
       <c r="F172" s="7"/>
     </row>
@@ -9607,7 +9708,7 @@
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
+      <c r="D173" s="21"/>
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
     </row>
@@ -9615,7 +9716,7 @@
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
-      <c r="D174" s="7"/>
+      <c r="D174" s="21"/>
       <c r="E174" s="7"/>
       <c r="F174" s="7"/>
     </row>
@@ -9623,7 +9724,7 @@
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
+      <c r="D175" s="21"/>
       <c r="E175" s="8"/>
       <c r="F175" s="8"/>
     </row>
@@ -9631,7 +9732,7 @@
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
-      <c r="D176" s="7"/>
+      <c r="D176" s="21"/>
       <c r="E176" s="7"/>
       <c r="F176" s="7"/>
     </row>
@@ -9639,7 +9740,7 @@
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
+      <c r="D177" s="21"/>
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
     </row>
@@ -9647,7 +9748,7 @@
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
-      <c r="D178" s="7"/>
+      <c r="D178" s="21"/>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
     </row>
@@ -9655,7 +9756,7 @@
       <c r="A179" s="8"/>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
+      <c r="D179" s="21"/>
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
     </row>
@@ -9663,7 +9764,7 @@
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
-      <c r="D180" s="7"/>
+      <c r="D180" s="21"/>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
     </row>
@@ -9671,7 +9772,7 @@
       <c r="A181" s="8"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
+      <c r="D181" s="21"/>
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
     </row>
@@ -9679,7 +9780,7 @@
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
-      <c r="D182" s="7"/>
+      <c r="D182" s="21"/>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
     </row>
@@ -9687,7 +9788,7 @@
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
+      <c r="D183" s="21"/>
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
     </row>
@@ -9695,7 +9796,7 @@
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
-      <c r="D184" s="7"/>
+      <c r="D184" s="21"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
     </row>
@@ -9703,7 +9804,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
+      <c r="D185" s="21"/>
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
     </row>
@@ -9711,7 +9812,7 @@
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
-      <c r="D186" s="7"/>
+      <c r="D186" s="21"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
     </row>
@@ -9719,7 +9820,7 @@
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
+      <c r="D187" s="21"/>
       <c r="E187" s="8"/>
       <c r="F187" s="8"/>
     </row>
@@ -9727,7 +9828,7 @@
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
-      <c r="D188" s="7"/>
+      <c r="D188" s="21"/>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
     </row>
@@ -9735,7 +9836,7 @@
       <c r="A189" s="8"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
+      <c r="D189" s="21"/>
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
     </row>
@@ -9743,7 +9844,7 @@
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
-      <c r="D190" s="7"/>
+      <c r="D190" s="21"/>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
     </row>
@@ -9751,7 +9852,7 @@
       <c r="A191" s="8"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
+      <c r="D191" s="21"/>
       <c r="E191" s="8"/>
       <c r="F191" s="8"/>
     </row>
@@ -9759,7 +9860,7 @@
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
-      <c r="D192" s="7"/>
+      <c r="D192" s="21"/>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
     </row>
@@ -9767,7 +9868,7 @@
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
+      <c r="D193" s="21"/>
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
     </row>
@@ -9775,7 +9876,7 @@
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
-      <c r="D194" s="7"/>
+      <c r="D194" s="21"/>
       <c r="E194" s="7"/>
       <c r="F194" s="7"/>
     </row>
@@ -9783,7 +9884,7 @@
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
+      <c r="D195" s="21"/>
       <c r="E195" s="8"/>
       <c r="F195" s="8"/>
     </row>
@@ -9791,7 +9892,7 @@
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
-      <c r="D196" s="7"/>
+      <c r="D196" s="21"/>
       <c r="E196" s="7"/>
       <c r="F196" s="7"/>
     </row>
@@ -9799,7 +9900,7 @@
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
+      <c r="D197" s="21"/>
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
     </row>
@@ -9807,7 +9908,7 @@
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
-      <c r="D198" s="7"/>
+      <c r="D198" s="21"/>
       <c r="E198" s="7"/>
       <c r="F198" s="7"/>
     </row>
@@ -9815,7 +9916,7 @@
       <c r="A199" s="8"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
+      <c r="D199" s="21"/>
       <c r="E199" s="8"/>
       <c r="F199" s="8"/>
     </row>
@@ -9823,7 +9924,7 @@
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
-      <c r="D200" s="7"/>
+      <c r="D200" s="21"/>
       <c r="E200" s="7"/>
       <c r="F200" s="7"/>
     </row>
@@ -9831,7 +9932,7 @@
       <c r="A201" s="8"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
-      <c r="D201" s="8"/>
+      <c r="D201" s="21"/>
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
     </row>
